--- a/marketing_report/outputs/Posgrados/Otros_Reportes/reporte_journey_tiempos.xlsx
+++ b/marketing_report/outputs/Posgrados/Otros_Reportes/reporte_journey_tiempos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L169"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,42 +549,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DNI_20248891.0</t>
+          <t>DNI_2120618.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Selva Vanesa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20248891</v>
+        <v>2120618</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45627</v>
+        <v>46068</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>374</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -601,32 +599,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DNI_2120618.0</t>
+          <t>DNI_2181822.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Selva Vanesa</t>
+          <t>Viviana</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2120618</v>
+        <v>2181822</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -653,42 +649,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DNI_21787699.0</t>
+          <t>DNI_2242819.0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>Reynaldo Gaston</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21787699</v>
+        <v>2242819</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45628</v>
+        <v>46079</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G5" t="n">
-        <v>367</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -705,32 +699,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DNI_2181822.0</t>
+          <t>DNI_2264822.0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viviana</t>
+          <t>Luciana</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2181822</v>
+        <v>2264822</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46071</v>
+        <v>46080</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -757,47 +749,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DNI_21916147.0</t>
+          <t>DNI_22946409.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21916147</v>
+        <v>22946409</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45629</v>
+        <v>45890</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45993</v>
-      </c>
-      <c r="G7" t="n">
-        <v>364</v>
-      </c>
+        <v>46007</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>3.0 -&gt; 3.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -809,47 +799,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DNI_2242819.0</t>
+          <t>DNI_24790890.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reynaldo Gaston</t>
+          <t>ANDREA VIVIANA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2242819</v>
+        <v>24790890</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46079</v>
+        <v>45866</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
+        <v>45961</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>3.0 -&gt; Desconocido</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -861,47 +849,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DNI_22946409.0</t>
+          <t>DNI_25009560.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GABRIELA SILVANA</t>
+          <t>Gladis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22946409</v>
+        <v>25009560</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>45659</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>46007</v>
-      </c>
-      <c r="G9" t="n">
-        <v>348</v>
-      </c>
+        <v>46001</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>3.0 -&gt; 477.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>477.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -913,47 +897,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DNI_23130229.0</t>
+          <t>DNI_25118778.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MERCEDES</t>
+          <t>pamela reyes alonso</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23130229</v>
+        <v>25118778</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45630</v>
+        <v>45826</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G10" t="n">
-        <v>378</v>
-      </c>
+        <v>45989</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>18.0 -&gt; 3.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -965,42 +947,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DNI_24790890.0</t>
+          <t>DNI_25457311.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Andrea Viviana</t>
+          <t>Rodrigo Daniel</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24790890</v>
+        <v>25457311</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>45957</v>
+        <v>46080</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45961</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1017,120 +997,114 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DNI_25009560.0</t>
+          <t>DNI_26057054.0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gladis</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25009560</v>
+        <v>26057054</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45909</v>
+        <v>46029</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="G12" t="n">
-        <v>92</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.0 -&gt; 477.0</t>
+          <t>907.0 -&gt; 37.0 -&gt; 37.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>477.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>37.0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DNI_25118778.0</t>
+          <t>DNI_26131584.0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pamela reyes alonso</t>
+          <t>carolina ortiz</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25118778</v>
+        <v>26131584</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>45634</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>45989</v>
-      </c>
-      <c r="G13" t="n">
-        <v>355</v>
-      </c>
+        <v>46017</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0 -&gt; 18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DNI_25457311.0</t>
+          <t>DNI_26936108.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rodrigo Daniel</t>
+          <t>Lucio Gabriel</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25457311</v>
+        <v>26936108</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1141,12 +1115,10 @@
       <c r="F14" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1173,21 +1145,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DNI_25496190.0</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>DNI_28566147.0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>María soledad</t>
+        </is>
+      </c>
       <c r="C15" t="n">
-        <v>25496190</v>
+        <v>28566147</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" s="2" t="n">
+        <v>46074</v>
+      </c>
       <c r="F15" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>46030</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1195,12 +1175,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1217,47 +1197,45 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DNI_25970546.0</t>
+          <t>DNI_29336116.0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marcela alejandra</t>
+          <t>Miguel Pereyra</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25970546</v>
+        <v>29336116</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45644</v>
+        <v>46023</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>46038</v>
-      </c>
-      <c r="G16" t="n">
-        <v>394</v>
-      </c>
+        <v>46029</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>907.0 -&gt; 907.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1269,28 +1247,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DNI_26057054.0</t>
+          <t>DNI_30103833.0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>LUCAS GABRIEL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26057054</v>
+        <v>30103833</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45656</v>
+        <v>46078</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>46052</v>
+        <v>45989</v>
       </c>
       <c r="G17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1299,17 +1277,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>37.0 -&gt; 37.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1321,99 +1299,95 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DNI_26131584.0</t>
+          <t>DNI_30348383.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>carolina ortiz</t>
+          <t>Elias Santiago</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26131584</v>
+        <v>30348383</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45649</v>
+        <v>46074</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="G18" t="n">
-        <v>368</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18.0 -&gt; 18.0 -&gt; 18.0</t>
+          <t>3.0 -&gt; 3.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DNI_26936108.0</t>
+          <t>DNI_30766482.0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lucio Gabriel</t>
+          <t>Maria Belen</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26936108</v>
+        <v>30766482</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46080</v>
+        <v>46023</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>3.0 -&gt; 3.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>3.0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1425,42 +1399,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DNI_28704348.0</t>
+          <t>DNI_30806219.0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Laura Natalia</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28704348</v>
+        <v>30806219</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>45654</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>46022</v>
-      </c>
-      <c r="G20" t="n">
-        <v>368</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1477,42 +1447,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DNI_28764685.0</t>
+          <t>DNI_31788443.0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Leonardo Andrés</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28764685</v>
+        <v>31788443</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45628</v>
+        <v>45831</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="G21" t="n">
-        <v>363</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1529,32 +1497,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DNI_29388311.0</t>
+          <t>DNI_31949090.0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maricel</t>
+          <t>Dana Macarena</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29388311</v>
+        <v>31949090</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45627</v>
+        <v>45750</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G22" t="n">
-        <v>429</v>
-      </c>
+        <v>46044</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1581,29 +1547,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DNI_29835996.0</t>
+          <t>DNI_32534579.0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RINA</t>
+          <t>Mercedes Soledad</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29835996</v>
+        <v>32534579</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>45637</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>46064</v>
-      </c>
-      <c r="G23" t="n">
-        <v>427</v>
-      </c>
+        <v>46013</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1611,12 +1573,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1633,32 +1595,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DNI_30221331.0</t>
+          <t>DNI_32914047.0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Carolina Mercedes</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>30221331</v>
+        <v>32914047</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45645</v>
+        <v>46078</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45986</v>
-      </c>
-      <c r="G24" t="n">
-        <v>341</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1685,47 +1645,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DNI_30348383.0</t>
+          <t>DNI_33753144.0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Elias Santiago</t>
+          <t>Anahí Rebeca</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30348383</v>
+        <v>33753144</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>46074</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
+        <v>46024</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.0 -&gt; 3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1737,84 +1693,76 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DNI_30644595.0</t>
+          <t>DNI_34524241.0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Augusto</t>
+          <t>Fernando Ezequiel</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30644595</v>
+        <v>34524241</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>45628</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>46007</v>
-      </c>
-      <c r="G26" t="n">
-        <v>379</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>103.0 -&gt; 4.0 -&gt; 503.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>503.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DNI_30806219.0</t>
+          <t>DNI_35482130.0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Yamila</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30806219</v>
+        <v>35482130</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>45681</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G27" t="n">
-        <v>375</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1841,42 +1789,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DNI_32534579.0</t>
+          <t>DNI_35599473.0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mercedes Soledad</t>
+          <t>VICTORIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32534579</v>
+        <v>35599473</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45659</v>
+        <v>46049</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>46013</v>
-      </c>
-      <c r="G28" t="n">
-        <v>354</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1893,32 +1839,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DNI_32914047.0</t>
+          <t>DNI_36345824.0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Pablo Alejandro</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>32914047</v>
+        <v>36345824</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>46078</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
+        <v>45989</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1945,21 +1887,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DNI_33168313.0</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>DNI_36379096.0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Marcela  Alejandra</t>
+        </is>
+      </c>
       <c r="C30" t="n">
-        <v>33168313</v>
+        <v>36379096</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" s="2" t="n">
+        <v>45740</v>
+      </c>
       <c r="F30" s="2" t="n">
-        <v>46043</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+        <v>46062</v>
+      </c>
+      <c r="G30" t="n">
+        <v>322</v>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1967,12 +1917,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1989,28 +1939,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DNI_33249793.0</t>
+          <t>DNI_37105548.0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Natalia Soledad</t>
+          <t>Flavia Fernanda</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>33249793</v>
+        <v>37105548</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45630</v>
+        <v>45816</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45987</v>
+        <v>46053</v>
       </c>
       <c r="G31" t="n">
-        <v>357</v>
+        <v>237</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2019,12 +1969,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2041,12 +1991,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DNI_33674543.0</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>DNI_38032739.0</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
       <c r="C32" t="n">
-        <v>33674543</v>
+        <v>38032739</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
@@ -2058,22 +2012,22 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Desconocido -&gt; Desconocido</t>
+          <t>18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2085,28 +2039,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DNI_33683194.0</t>
+          <t>DNI_38035015.0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rodolfo</t>
+          <t>GABRIELA BEATRIZ</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>33683194</v>
+        <v>38035015</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45636</v>
+        <v>45860</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="G33" t="n">
-        <v>388</v>
+        <v>171</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2115,12 +2069,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2137,47 +2091,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DNI_33753144.0</t>
+          <t>DNI_38738650.0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Anahí Rebeca</t>
+          <t>Mariana</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33753144</v>
+        <v>38738650</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>45639</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>46024</v>
-      </c>
-      <c r="G34" t="n">
-        <v>385</v>
-      </c>
+        <v>46032</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0 -&gt; 3.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2189,42 +2139,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DNI_33885494.0</t>
+          <t>DNI_39004179.0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Florencia</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>33885494</v>
+        <v>39004179</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>45628</v>
+        <v>46042</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G35" t="n">
-        <v>382</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2241,42 +2189,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DNI_34272692.0</t>
+          <t>DNI_39320904.0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>natalia</t>
+          <t>German</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34272692</v>
+        <v>39320904</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>45627</v>
+        <v>45810</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G36" t="n">
-        <v>368</v>
-      </c>
+        <v>46008</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>477.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>477.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2293,42 +2239,38 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DNI_34399845.0</t>
+          <t>DNI_40934003.0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Martin Eduardo</t>
+          <t>Camila Florencia</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>34399845</v>
+        <v>40934003</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>45636</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>46027</v>
-      </c>
-      <c r="G37" t="n">
-        <v>391</v>
-      </c>
+        <v>46066</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2345,94 +2287,86 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DNI_34524241.0</t>
+          <t>DNI_40934059.0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fernando Ezequiel</t>
+          <t>Lucas Freytes de los Rios</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>34524241</v>
+        <v>40934059</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>45634</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>46058</v>
-      </c>
-      <c r="G38" t="n">
-        <v>424</v>
-      </c>
+        <v>46008</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>103.0 -&gt; 4.0 -&gt; 503.0</t>
+          <t>3.0 -&gt; 3.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>503.0</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DNI_34860000.0</t>
+          <t>DNI_41035709.0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dina</t>
+          <t>Melanie Antonella</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34860000</v>
+        <v>41035709</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>45671</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>46055</v>
-      </c>
-      <c r="G39" t="n">
-        <v>384</v>
-      </c>
+        <v>46021</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2449,42 +2383,40 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DNI_35482130.0</t>
+          <t>DNI_44327105.0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yamila</t>
+          <t>Yanci</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>35482130</v>
+        <v>44327105</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>45652</v>
+        <v>45819</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>46059</v>
-      </c>
-      <c r="G40" t="n">
-        <v>407</v>
-      </c>
+        <v>46006</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2501,29 +2433,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DNI_36345824.0</t>
+          <t>DNI_44744527.0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pablo Alejandro</t>
+          <t>FACUNDO SANTIAGO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>36345824</v>
+        <v>44744527</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>45985</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="n">
-        <v>45989</v>
-      </c>
-      <c r="G41" t="n">
-        <v>4</v>
-      </c>
+        <v>45992</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2531,12 +2459,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2553,34 +2481,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DNI_36808744.0</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>DNI_4518359.0</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PABLO</t>
+        </is>
+      </c>
       <c r="C42" t="n">
-        <v>36808744</v>
+        <v>4518359</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" s="2" t="n">
+        <v>46080</v>
+      </c>
       <c r="F42" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2597,28 +2531,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DNI_37745055.0</t>
+          <t>DNI_45849671.0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gabriela Natalia</t>
+          <t>Mariana</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37745055</v>
+        <v>45849671</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>45643</v>
+        <v>45870</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>46003</v>
+        <v>46027</v>
       </c>
       <c r="G43" t="n">
-        <v>360</v>
+        <v>157</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2627,12 +2561,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2649,47 +2583,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DNI_38032739.0</t>
+          <t>DNI_4658448.0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Paola</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38032739</v>
+        <v>4658448</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>45688</v>
+        <v>46074</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="G44" t="n">
-        <v>321</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>18.0 -&gt; 18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2701,42 +2633,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DNI_38136694.0</t>
+          <t>DNI_4869437.0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Yamila</t>
+          <t>Noem</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38136694</v>
+        <v>4869437</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>45627</v>
+        <v>46081</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>46002</v>
-      </c>
-      <c r="G45" t="n">
-        <v>375</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2753,37 +2683,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DNI_38738650.0</t>
+          <t>DNI_5679726.0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38738650</v>
+        <v>5679726</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>45913</v>
+        <v>46073</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="G46" t="n">
-        <v>119</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.0 -&gt; 3.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2793,7 +2721,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2805,28 +2733,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DNI_39058312.0</t>
+          <t>EMAIL_acbaires@gmail.com</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Julieta</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>39058312</v>
-      </c>
+          <t>Ale cesar</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>45627</v>
+        <v>46043</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>46003</v>
+        <v>46037</v>
       </c>
       <c r="G47" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2835,12 +2761,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2857,42 +2783,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DNI_39208522.0</t>
+          <t>EMAIL_agustinaliendro495@gmail.com</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Maria Victoria</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>39208522</v>
-      </c>
+          <t>Milagros Agustina</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>45627</v>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G48" t="n">
-        <v>383</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2909,21 +2829,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DNI_39536372.0</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="n">
-        <v>39536372</v>
-      </c>
+          <t>EMAIL_alejandrafabian53@gmail.com</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lucia Lucia</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" s="2" t="n">
+        <v>45856</v>
+      </c>
       <c r="F49" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+        <v>46007</v>
+      </c>
+      <c r="G49" t="n">
+        <v>151</v>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2931,12 +2857,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2953,28 +2879,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DNI_40934003.0</t>
+          <t>EMAIL_anabmx@hotmail.com</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Camila Florencia</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>40934003</v>
-      </c>
+          <t>Anita Heredia</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>45911</v>
+        <v>46024</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>46066</v>
+        <v>45988</v>
       </c>
       <c r="G50" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2983,17 +2907,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Desconocido -&gt; Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3005,47 +2929,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DNI_40934059.0</t>
+          <t>EMAIL_antonellatoloza05@gmail.com</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lucas Freytes de los Rios</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>40934059</v>
-      </c>
+          <t>ANTONELLA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>45987</v>
+        <v>45867</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G51" t="n">
-        <v>21</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3.0 -&gt; 3.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3057,28 +2977,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DNI_41035709.0</t>
+          <t>EMAIL_barloquimari@gmail.com</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Melanie Antonella</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>41035709</v>
-      </c>
+          <t>Maria victoria</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>45929</v>
+        <v>46078</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="G52" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3087,12 +3005,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3109,42 +3027,38 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DNI_41390870.0</t>
+          <t>EMAIL_bartolini.david@outlook.com</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Teresa</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>41390870</v>
-      </c>
+          <t>Angel Bartolini</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>45629</v>
+        <v>46073</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45993</v>
-      </c>
-      <c r="G53" t="n">
-        <v>364</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3161,42 +3075,36 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DNI_41654113.0</t>
+          <t>EMAIL_carinavillalva@hotmail.com.ar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>vicente</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>41654113</v>
-      </c>
+          <t>Caru Villalva</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>45655</v>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G54" t="n">
-        <v>397</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3213,39 +3121,41 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DNI_41718618.0</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
-        <v>41718618</v>
-      </c>
+          <t>EMAIL_cesar3.arevalo@gmail.com</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Arevalo Cesar</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" s="2" t="n">
-        <v>46052</v>
+        <v>46009</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3257,42 +3167,38 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DNI_41985133.0</t>
+          <t>EMAIL_cesaraveron1@gmail.com</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Florencia Mariel</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>41985133</v>
-      </c>
+          <t>CESAR A</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>45645</v>
+        <v>46074</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>46031</v>
-      </c>
-      <c r="G56" t="n">
-        <v>386</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3309,42 +3215,38 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DNI_42717270.0</t>
+          <t>EMAIL_chiaramonteluciano@hotmail.com</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>42717270</v>
-      </c>
+          <t>Luciano Chiaramonte de Clermont</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>45629</v>
+        <v>45831</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="G57" t="n">
-        <v>388</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3361,29 +3263,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DNI_43337181.0</t>
+          <t>EMAIL_claufaran79@gmail.com</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Andrea</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>43337181</v>
-      </c>
+          <t>Claudio Fabian Arancibia</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>45627</v>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G58" t="n">
-        <v>383</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3391,12 +3287,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3413,34 +3309,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DNI_43375713.0</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="n">
-        <v>43375713</v>
-      </c>
+          <t>EMAIL_colqueveronica1@gmail.com</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Adriana Rueda</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3457,42 +3355,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DNI_44346837.0</t>
+          <t>EMAIL_cristianlopezla12@gmail.com</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rosa</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>44346837</v>
-      </c>
+          <t>Cristian Emanuel Lopez</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>45632</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" s="2" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G60" t="n">
-        <v>397</v>
-      </c>
+        <v>46064</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3509,39 +3401,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DNI_44578755.0</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="n">
-        <v>44578755</v>
-      </c>
+          <t>EMAIL_daiferperez89@gmail.com</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Daisi Fernanda Perez</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" s="2" t="n">
-        <v>46052</v>
+        <v>46009</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3553,34 +3447,36 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DNI_44845417.0</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="n">
-        <v>44845417</v>
-      </c>
+          <t>EMAIL_danielalorena751@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Dani Martinez</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
         <v>1</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="2" t="n">
-        <v>46052</v>
+        <v>46031</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3597,47 +3493,43 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DNI_44878428.0</t>
+          <t>EMAIL_daromontero@gmail.com</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Esteban</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>44878428</v>
-      </c>
+          <t>DARIO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>45634</v>
+        <v>45849</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>46049</v>
-      </c>
-      <c r="G63" t="n">
-        <v>415</v>
-      </c>
+        <v>46009</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0 -&gt; 3.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3649,42 +3541,36 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DNI_45432189.0</t>
+          <t>EMAIL_eliasdavidperez0@gmail.com</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Candela</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>45432189</v>
-      </c>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>45628</v>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="G64" t="n">
-        <v>393</v>
-      </c>
+        <v>46049</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3701,39 +3587,43 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DNI_45975204.0</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="n">
-        <v>45975204</v>
-      </c>
+          <t>EMAIL_elizabethz3016@gmail.com</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Valeria</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>46074</v>
+      </c>
       <c r="F65" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3745,34 +3635,38 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DNI_46171341.0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="n">
-        <v>46171341</v>
-      </c>
+          <t>EMAIL_emilopez1985@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Emi Lopez</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" s="2" t="n">
+        <v>46076</v>
+      </c>
       <c r="F66" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3789,21 +3683,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DNI_46531477.0</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="n">
-        <v>46531477</v>
-      </c>
+          <t>EMAIL_ezegero24@gmail.com</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MATÍAS EZEQUIEL</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" s="2" t="n">
+        <v>46033</v>
+      </c>
       <c r="F67" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
+        <v>45991</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3811,12 +3711,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3833,47 +3733,43 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DNI_4658448.0</t>
+          <t>EMAIL_fgimenez@ucasal.edu.ar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Paola</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>4658448</v>
-      </c>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>46074</v>
+        <v>46021</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
+        <v>46024</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>908.0 -&gt; 443.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>908.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>443.0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3885,34 +3781,38 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DNI_46801371.0</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="n">
-        <v>46801371</v>
-      </c>
+          <t>EMAIL_florcalabrese@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Flori</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" s="2" t="n">
+        <v>45784</v>
+      </c>
       <c r="F69" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3929,28 +3829,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DNI_47150637.0</t>
+          <t>EMAIL_florenciamariel02@gmail.com</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lara</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>47150637</v>
-      </c>
+          <t>Florencia mariel</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>45627</v>
+        <v>45745</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>46010</v>
+        <v>46031</v>
       </c>
       <c r="G70" t="n">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3959,12 +3857,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3981,21 +3879,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DNI_47450082.0</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="n">
-        <v>47450082</v>
-      </c>
+          <t>EMAIL_florzapatiel13@gmail.com</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Florencia Alejandra</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" s="2" t="n">
+        <v>46056</v>
+      </c>
       <c r="F71" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
+        <v>46023</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -4003,12 +3907,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4025,21 +3929,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DNI_47450605.0</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="n">
-        <v>47450605</v>
-      </c>
+          <t>EMAIL_francomiranda297@gmail.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" s="2" t="n">
+        <v>46037</v>
+      </c>
       <c r="F72" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
+        <v>46029</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -4047,12 +3957,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4069,39 +3979,43 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DNI_48006326.0</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="n">
-        <v>48006326</v>
-      </c>
+          <t>EMAIL_frovastefano@gmail.com</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Stefano Frova</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>45872</v>
+      </c>
       <c r="F73" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4113,34 +4027,36 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DNI_48084522.0</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="n">
-        <v>48084522</v>
-      </c>
+          <t>EMAIL_gaby.acchurallanos@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gabriela Acchura Llanos</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" s="2" t="n">
-        <v>46052</v>
+        <v>46010</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4157,21 +4073,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DNI_48208302.0</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="n">
-        <v>48208302</v>
-      </c>
+          <t>EMAIL_geor_e_@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Georgina</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" s="2" t="n">
+        <v>46029</v>
+      </c>
       <c r="F75" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G75" t="inlineStr"/>
+        <v>46008</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -4179,12 +4101,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4201,21 +4123,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DNI_48209642.0</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="n">
-        <v>48209642</v>
-      </c>
+          <t>EMAIL_giulianamendoza30@gmail.com</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>giuliana antonella</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
         <v>1</v>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" s="2" t="n">
+        <v>46052</v>
+      </c>
       <c r="F76" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G76" t="inlineStr"/>
+        <v>46010</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -4223,12 +4151,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4245,21 +4173,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DNI_48278814.0</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="n">
-        <v>48278814</v>
-      </c>
+          <t>EMAIL_hijoteamo375@gmail.com</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Susana Susana</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" s="2" t="n">
+        <v>46023</v>
+      </c>
       <c r="F77" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G77" t="inlineStr"/>
+        <v>46064</v>
+      </c>
+      <c r="G77" t="n">
+        <v>41</v>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -4267,12 +4201,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4289,34 +4223,36 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DNI_48289797.0</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="n">
-        <v>48289797</v>
-      </c>
+          <t>EMAIL_hormitaki@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Celeste Rodriguez Simon</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4333,34 +4269,38 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DNI_48517610.0</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="n">
-        <v>48517610</v>
-      </c>
+          <t>EMAIL_jorgeandresburgos82@gmail.com</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mejorge</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" s="2" t="n">
+        <v>46064</v>
+      </c>
       <c r="F79" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4377,34 +4317,38 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DNI_48518369.0</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="n">
-        <v>48518369</v>
-      </c>
+          <t>EMAIL_jorgelinap300@gmail.com</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Jorgelina</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" s="2" t="n">
+        <v>46039</v>
+      </c>
       <c r="F80" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4421,13 +4365,15 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DNI_48519429.0</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="n">
-        <v>48519429</v>
-      </c>
+          <t>EMAIL_julimaol@gmail.com</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
         <v>1</v>
       </c>
@@ -4438,17 +4384,17 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4465,21 +4411,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DNI_48777847.0</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="n">
-        <v>48777847</v>
-      </c>
+          <t>EMAIL_karitofierro78@gmail.com</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Carolina Mercedes</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" s="2" t="n">
+        <v>45734</v>
+      </c>
       <c r="F82" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>45986</v>
+      </c>
+      <c r="G82" t="n">
+        <v>252</v>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -4487,12 +4439,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4509,21 +4461,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DNI_48778601.0</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="n">
-        <v>48778601</v>
-      </c>
+          <t>EMAIL_lauraesposto@hotmail.com</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Laura Esposto</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>2</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>46017</v>
+      </c>
       <c r="F83" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
+        <v>46011</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -4531,17 +4489,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Desconocido -&gt; Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4553,13 +4511,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DNI_48779579.0</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="n">
-        <v>48779579</v>
-      </c>
+          <t>EMAIL_leivacarinaf@gmail.com</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Carina leiva</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
         <v>1</v>
       </c>
@@ -4570,17 +4530,17 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4597,34 +4557,34 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DNI_48917553.0</t>
+          <t>EMAIL_licmarcelamamani@gmail.com</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
-      <c r="C85" t="n">
-        <v>48917553</v>
-      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
         <v>1</v>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" s="2" t="n">
+        <v>46069</v>
+      </c>
       <c r="F85" s="2" t="n">
-        <v>46056</v>
+        <v>46031</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4641,42 +4601,36 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DNI_5679726.0</t>
+          <t>EMAIL_luuciazambrano@gmail.com</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>5679726</v>
-      </c>
+          <t>Luu Zambrano</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>46073</v>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
+        <v>46010</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4693,30 +4647,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EMAIL_abigail_9021@hotmail.com</t>
+          <t>EMAIL_marceteje1304@gmail.com</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vanesa Veronica</t>
+          <t>Marcela Alejandra Tejerina</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>45642</v>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" s="2" t="n">
-        <v>45993</v>
-      </c>
-      <c r="G87" t="n">
-        <v>351</v>
-      </c>
+        <v>45992</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4743,12 +4693,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EMAIL_agustinaliendro495@gmail.com</t>
+          <t>EMAIL_marialaurabuono@gmail.com</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Milagros Agustina</t>
+          <t>Maria Laura</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -4756,17 +4706,15 @@
         <v>1</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>45913</v>
+        <v>45840</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G88" t="n">
-        <v>139</v>
-      </c>
+        <v>46001</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4793,12 +4741,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EMAIL_alejandrachavez7225@gmail.com</t>
+          <t>EMAIL_maricelcayata@gmail.com</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Alejandra Chavez</t>
+          <t>Maricel</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -4806,27 +4754,25 @@
         <v>1</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>45988</v>
+        <v>45864</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>46024</v>
-      </c>
-      <c r="G89" t="n">
-        <v>36</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4843,45 +4789,41 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EMAIL_antonellagiuliana811@gmail.com</t>
+          <t>EMAIL_mariselguerrero3@gmail.com</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Giuliana Antonella</t>
+          <t>Guerrero Cabezas Marisel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>45989</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G90" t="n">
-        <v>21</v>
-      </c>
+        <v>46001</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -4893,40 +4835,36 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EMAIL_bartolini.david@outlook.com</t>
+          <t>EMAIL_matias.orellan@gmail.com</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Angel Bartolini</t>
+          <t>Mati Orellana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>46073</v>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4943,12 +4881,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EMAIL_carinavillalva@hotmail.com.ar</t>
+          <t>EMAIL_mauriv10481@yahoo.com.ar</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Caru Villalva</t>
+          <t>MAURO FEDERICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -4956,13 +4894,13 @@
         <v>1</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>45652</v>
+        <v>46057</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>46056</v>
+        <v>46009</v>
       </c>
       <c r="G92" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4971,12 +4909,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4993,12 +4931,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EMAIL_cc.cecyislas@gmail.com</t>
+          <t>EMAIL_mbasualdo200@gmail.com</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cecilia  Carletti</t>
+          <t>Anto</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -5006,13 +4944,13 @@
         <v>1</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>45991</v>
+        <v>46071</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>46052</v>
+        <v>45986</v>
       </c>
       <c r="G93" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -5043,40 +4981,36 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EMAIL_cedalessa@yahoo.com</t>
+          <t>EMAIL_melizanolasco360@gmail.com</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>nolasco meliza</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>45629</v>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="G94" t="n">
-        <v>392</v>
-      </c>
+        <v>46008</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5093,35 +5027,31 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EMAIL_cesar3.arevalo@gmail.com</t>
+          <t>EMAIL_micaelalotufo@gmail.com</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Arevalo Cesar</t>
+          <t>Micaela Lotufo Haddad</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>2</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>45633</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="G95" t="n">
-        <v>376</v>
-      </c>
+        <v>46044</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>18.0 -&gt; 18.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5131,7 +5061,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5143,12 +5073,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EMAIL_cesaraveron1@gmail.com</t>
+          <t>EMAIL_nadita_27@hotmail.com.ar</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CESAR A</t>
+          <t>Nadia Garcia</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -5156,13 +5086,13 @@
         <v>1</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>46074</v>
+        <v>45872</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>46052</v>
+        <v>46050</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -5171,12 +5101,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5193,12 +5123,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EMAIL_chudchus087@gmail.com</t>
+          <t>EMAIL_nataliaevillarreal2019@gmail.com</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Maria Molina Molina</t>
+          <t>Natalia Natalia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -5206,13 +5136,13 @@
         <v>1</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>45935</v>
+        <v>46040</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>46062</v>
+        <v>45995</v>
       </c>
       <c r="G97" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5243,12 +5173,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EMAIL_cm139730@gmail.com</t>
+          <t>EMAIL_nataliasoledadcejas02@gmail.com</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sebastian Miranda</t>
+          <t>Claudio lucas primero</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -5256,13 +5186,13 @@
         <v>1</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>45660</v>
+        <v>46042</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>46029</v>
+        <v>45987</v>
       </c>
       <c r="G98" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5293,12 +5223,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EMAIL_colqueveronica1@gmail.com</t>
+          <t>EMAIL_natischmid76@gmail.com</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Adriana Rueda</t>
+          <t>Natalia Erika Schmid</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -5306,13 +5236,13 @@
         <v>1</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>45904</v>
+        <v>46058</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>46056</v>
+        <v>46065</v>
       </c>
       <c r="G99" t="n">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -5343,40 +5273,34 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EMAIL_cr4674@gmail.com</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Eliana Rodriguez</t>
-        </is>
-      </c>
+          <t>EMAIL_nelsonrubenpereira1327@gmail.com</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>45665</v>
+        <v>46063</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>46020</v>
-      </c>
-      <c r="G100" t="n">
-        <v>355</v>
-      </c>
+        <v>45989</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5393,30 +5317,26 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EMAIL_cristianlopezla12@gmail.com</t>
+          <t>EMAIL_noali_84@hotmail.com</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cristian Emanuel Lopez</t>
+          <t>Noali Elisabeth Garcia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>45634</v>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" s="2" t="n">
-        <v>46064</v>
-      </c>
-      <c r="G101" t="n">
-        <v>430</v>
-      </c>
+        <v>46000</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5443,30 +5363,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EMAIL_daiferperez89@gmail.com</t>
+          <t>EMAIL_noe_abril_89@hotmail.com</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Daisi Fernanda Perez</t>
+          <t>Noelia Ruiz</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
         <v>2</v>
       </c>
-      <c r="E102" s="2" t="n">
-        <v>45911</v>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="G102" t="n">
-        <v>98</v>
-      </c>
+        <v>46062</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5493,30 +5409,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EMAIL_danielalorena751@hotmail.com</t>
+          <t>EMAIL_pablo.larocca@gmail.com</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dani Martinez</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>45925</v>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" s="2" t="n">
-        <v>46031</v>
-      </c>
-      <c r="G103" t="n">
-        <v>106</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5543,40 +5455,36 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EMAIL_eliasdavidperez0@gmail.com</t>
+          <t>EMAIL_pabloortiz_ar@live.com.ar</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Pablo Pablo Ortiz</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>45927</v>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" s="2" t="n">
-        <v>46049</v>
-      </c>
-      <c r="G104" t="n">
-        <v>122</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5593,35 +5501,31 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EMAIL_elizabethz3016@gmail.com</t>
+          <t>EMAIL_paorey06@live.com.ar</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Pao Rey</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>45978</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G105" t="n">
-        <v>74</v>
-      </c>
+        <v>45996</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>18.0 -&gt; 18.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5631,7 +5535,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5643,12 +5547,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EMAIL_emilopez1985@hotmail.com</t>
+          <t>EMAIL_paulandrrea43@hotmail.com</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Emi Lopez</t>
+          <t>Auchana Pau</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -5656,27 +5560,25 @@
         <v>1</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>46076</v>
+        <v>46027</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5693,30 +5595,26 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EMAIL_evan22.552@gmail.com</t>
+          <t>EMAIL_psicoprofe2017@gmail.com</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Evangelina Judith</t>
+          <t>Macarena Rodriguez</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
         <v>1</v>
       </c>
-      <c r="E107" s="2" t="n">
-        <v>45660</v>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" s="2" t="n">
-        <v>46003</v>
-      </c>
-      <c r="G107" t="n">
-        <v>343</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5743,30 +5641,26 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EMAIL_everricalde@gmail.com</t>
+          <t>EMAIL_pvuistaz@gmail.com</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Pamela Vuistaz</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
         <v>1</v>
       </c>
-      <c r="E108" s="2" t="n">
-        <v>45631</v>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" s="2" t="n">
-        <v>45997</v>
-      </c>
-      <c r="G108" t="n">
-        <v>366</v>
-      </c>
+        <v>46010</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5793,12 +5687,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EMAIL_florzapatiel13@gmail.com</t>
+          <t>EMAIL_rajoliliana@gmail.com</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Florencia Alejandra</t>
+          <t>LILIANA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -5806,27 +5700,25 @@
         <v>1</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>46056</v>
+        <v>45821</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -5843,12 +5735,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EMAIL_franzapata03@icloud.com</t>
+          <t>EMAIL_retamar.yamilaa@gmail.com</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fran</t>
+          <t>Yamila Retamar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -5856,27 +5748,25 @@
         <v>1</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>45646</v>
+        <v>46039</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46007</v>
-      </c>
-      <c r="G110" t="n">
-        <v>361</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5893,35 +5783,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EMAIL_frovastefano@gmail.com</t>
+          <t>EMAIL_retamozoliliana1407@gmail.com</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stefano Frova</t>
+          <t>Ly</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>45912</v>
+        <v>46029</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="G111" t="n">
-        <v>144</v>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5931,7 +5819,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -5943,35 +5831,31 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EMAIL_gaby.acchurallanos@hotmail.com</t>
+          <t>EMAIL_reynagadaniela116@gmail.com</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Gabriela Acchura Llanos</t>
+          <t>Daniela Reynaga</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>45942</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G112" t="n">
-        <v>68</v>
-      </c>
+        <v>46029</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.0 -&gt; 18.0 -&gt; 18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5981,24 +5865,24 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EMAIL_gonzaleznahuelleonel5@gmail.com</t>
+          <t>EMAIL_robertogareis@gmail.com</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Gonzalez Gonzalez</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -6006,27 +5890,25 @@
         <v>1</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>46057</v>
+        <v>45848</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6043,27 +5925,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EMAIL_gracielaquiroga153@hotmail.com</t>
+          <t>EMAIL_rociopelaez@outlook.com</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Graciela Quiroga</t>
+          <t>Rocio Pelaez</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>46076</v>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
+        <v>46003</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -6093,35 +5971,31 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EMAIL_hormitaki@hotmail.com</t>
+          <t>EMAIL_rodrigodjram@gmail.com</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Celeste Rodriguez Simon</t>
+          <t>Alejandro Ra</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>45973</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G115" t="n">
-        <v>83</v>
-      </c>
+        <v>46009</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.0 -&gt; 18.0</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6131,7 +6005,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6143,12 +6017,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EMAIL_hugoraulfantusatti@gmail.com</t>
+          <t>EMAIL_romanolaura.unqui@gmail.com</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>hugo</t>
+          <t>LAURA NATALIA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -6156,13 +6030,13 @@
         <v>1</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>45632</v>
+        <v>46041</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="G116" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -6171,12 +6045,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6193,12 +6067,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EMAIL_jara_ivana@yahoo.com</t>
+          <t>EMAIL_romibarrios9@gmail.com</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mariana Mariana</t>
+          <t>Romi B Banega</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -6206,17 +6080,15 @@
         <v>1</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>45904</v>
+        <v>45826</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45979</v>
-      </c>
-      <c r="G117" t="n">
-        <v>75</v>
-      </c>
+        <v>46042</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6243,12 +6115,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EMAIL_jessfrancoart@gmail.com</t>
+          <t>EMAIL_romina.sancheez@gmail.com</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jess</t>
+          <t>Romina Sanchez</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -6256,17 +6128,15 @@
         <v>1</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>45627</v>
+        <v>45844</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G118" t="n">
-        <v>383</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6293,12 +6163,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EMAIL_jorgeandresburgos82@gmail.com</t>
+          <t>EMAIL_rosymiamor758@gmail.com</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mejorge</t>
+          <t>Rosa del carmen</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -6306,13 +6176,13 @@
         <v>1</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>46064</v>
+        <v>46036</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>46056</v>
+        <v>46043</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -6321,12 +6191,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>625.0</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -6343,12 +6213,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EMAIL_julimaol@gmail.com</t>
+          <t>EMAIL_sciam740@gmail.com</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -6356,27 +6226,25 @@
         <v>1</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>45660</v>
+        <v>46058</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G120" t="n">
-        <v>392</v>
-      </c>
+        <v>45978</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>494.0</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>494.0</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -6393,30 +6261,26 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EMAIL_laupergamino@hotmail.com</t>
+          <t>EMAIL_solvaldez_25@hotmail.com</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Laura Laura Maria</t>
+          <t>Sol Valdez</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" s="2" t="n">
-        <v>45687</v>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" s="2" t="n">
-        <v>46011</v>
-      </c>
-      <c r="G121" t="n">
-        <v>324</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6443,12 +6307,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EMAIL_leivacarinaf@gmail.com</t>
+          <t>EMAIL_tamaguilar00@gmail.com</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Carina leiva</t>
+          <t>Tam</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -6456,27 +6320,25 @@
         <v>1</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>45930</v>
+        <v>46037</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G122" t="n">
-        <v>122</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -6493,36 +6355,38 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EMAIL_licmarcelamamani@gmail.com</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>EMAIL_tarcibarboza@gmail.com</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tarcicio Barboza</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
         <v>1</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>46069</v>
+        <v>45830</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>46031</v>
-      </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
+        <v>46052</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -6539,45 +6403,41 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EMAIL_lilibazan@live.com</t>
+          <t>EMAIL_tsvictoriavallejo@gmail.com</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Liliana Bazan</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>45957</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" s="2" t="n">
-        <v>46057</v>
-      </c>
-      <c r="G124" t="n">
-        <v>100</v>
-      </c>
+        <v>45989</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>4.0 -&gt; 4.0</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6589,30 +6449,26 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EMAIL_lucia22castellano@gmail.com</t>
+          <t>EMAIL_valeraquel79@gimail.com</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lucia Castellano</t>
+          <t>Valeria Raquel Pastrana</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
         <v>1</v>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>45975</v>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" s="2" t="n">
-        <v>46058</v>
-      </c>
-      <c r="G125" t="n">
-        <v>83</v>
-      </c>
+        <v>46041</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6639,27 +6495,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EMAIL_luciaagustina_12@hotmail.com</t>
+          <t>EMAIL_verocompe@gmail.com</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lucia</t>
+          <t>VERONICA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>45627</v>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" s="2" t="n">
-        <v>46003</v>
-      </c>
-      <c r="G126" t="n">
-        <v>376</v>
-      </c>
+        <v>46006</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -6689,12 +6541,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EMAIL_luuciazambrano@gmail.com</t>
+          <t>EMAIL_vidalmarcela388@gmail.com</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Luu Zambrano</t>
+          <t>Marcela Alejandra</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -6702,13 +6554,13 @@
         <v>1</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>45912</v>
+        <v>46072</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>46010</v>
+        <v>46038</v>
       </c>
       <c r="G127" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -6717,12 +6569,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6739,30 +6591,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EMAIL_mandatarioferreyraf@gmail.com</t>
+          <t>EMAIL_ydatri@gmail.com</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fernando Ferreyra</t>
+          <t>Ye</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>45654</v>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" s="2" t="n">
-        <v>46000</v>
-      </c>
-      <c r="G128" t="n">
-        <v>346</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6781,2052 +6629,6 @@
         </is>
       </c>
       <c r="L128" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>EMAIL_marcelamarfer@hotmail.com</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>MarceLa Fernandez</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>45654</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G129" t="n">
-        <v>354</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>EMAIL_marcelavara81@gmail.com</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Karen Gutierrez</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>45957</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>46037</v>
-      </c>
-      <c r="G130" t="n">
-        <v>80</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>EMAIL_marceteje1304@gmail.com</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Marcela Alejandra Tejerina</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>45639</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G131" t="n">
-        <v>353</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>EMAIL_mariselguerrero3@gmail.com</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Guerrero Cabezas Marisel</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="n">
-        <v>2</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="G132" t="n">
-        <v>93</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3.0 -&gt; 18.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>EMAIL_matias.orellan@gmail.com</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Mati Orellana</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>45659</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G133" t="n">
-        <v>397</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>EMAIL_maty1392@gmail.com</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Matías exequiel</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>45628</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>46055</v>
-      </c>
-      <c r="G134" t="n">
-        <v>427</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>EMAIL_mauriv10481@yahoo.com.ar</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>MAURO FEDERICO</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>46057</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>EMAIL_maxitar_01@hotmail.com.ar</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Maximiliano Arce</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>45684</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>46011</v>
-      </c>
-      <c r="G136" t="n">
-        <v>327</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>EMAIL_mcelestecaamano@gmail.com</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Maria Celeste Caamano</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>45982</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>45988</v>
-      </c>
-      <c r="G137" t="n">
-        <v>6</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>EMAIL_melizanolasco360@gmail.com</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>nolasco meliza</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>45984</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G138" t="n">
-        <v>24</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>EMAIL_micaelalotufo@gmail.com</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Micaela Lotufo Haddad</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>45902</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="G139" t="n">
-        <v>142</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>EMAIL_miraspaula1412@gmail.com</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Pau</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="G140" t="n">
-        <v>374</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>EMAIL_nachosalvatierra130@gmail.com</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>salvatierra ignacio</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>45685</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="G141" t="n">
-        <v>324</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>EMAIL_nadiagarcia183@gmail.com</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Nadia Garcia</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>45664</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>46050</v>
-      </c>
-      <c r="G142" t="n">
-        <v>386</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>EMAIL_nelsonrubenpereira1327@gmail.com</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>46063</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>45989</v>
-      </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>907.0</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>907.0</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>EMAIL_noali_84@hotmail.com</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Noali Elisabeth Garcia</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>45942</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>46000</v>
-      </c>
-      <c r="G144" t="n">
-        <v>58</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>EMAIL_noe_abril_89@hotmail.com</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Noelia Ruiz</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="n">
-        <v>2</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>45945</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="G145" t="n">
-        <v>117</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>18.0 -&gt; 18.0</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>EMAIL_pablo.larocca@gmail.com</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Pablo</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>45935</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G146" t="n">
-        <v>121</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>EMAIL_pabloortiz_ar@live.com.ar</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Pablo Pablo Ortiz</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>45676</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G147" t="n">
-        <v>376</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>EMAIL_paly_106@hotmail.com</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>45634</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>45988</v>
-      </c>
-      <c r="G148" t="n">
-        <v>354</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>EMAIL_paorey06@live.com.ar</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Pao Rey</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G149" t="n">
-        <v>36</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>EMAIL_portillogladys60@gmail.com</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Gladys</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>45628</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G150" t="n">
-        <v>380</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>EMAIL_psicoprofe2017@gmail.com</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Macarena Rodriguez</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>45980</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G151" t="n">
-        <v>72</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>EMAIL_pvuistaz@gmail.com</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Pamela Vuistaz</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>45913</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G152" t="n">
-        <v>97</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>EMAIL_retamozoliliana1407@gmail.com</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Ly</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>45906</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G153" t="n">
-        <v>150</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>EMAIL_reynagadaniela116@gmail.com</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Daniela Reynaga</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="n">
-        <v>4</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>45674</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G154" t="n">
-        <v>355</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>18.0 -&gt; 18.0 -&gt; 18.0 -&gt; 18.0</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>EMAIL_rociopelaez@outlook.com</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Rocio Pelaez</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>45683</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>46003</v>
-      </c>
-      <c r="G155" t="n">
-        <v>320</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>EMAIL_rodrigodjram@gmail.com</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Alejandro Ra</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="n">
-        <v>2</v>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>45670</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="G156" t="n">
-        <v>339</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>18.0 -&gt; 18.0</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>EMAIL_salvatierrayaki@gmail.com</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Eliana</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>46002</v>
-      </c>
-      <c r="G157" t="n">
-        <v>375</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>EMAIL_sciam740@gmail.com</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>GABRIELA</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" s="2" t="n">
-        <v>46058</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>45978</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>494.0</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>494.0</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>EMAIL_sofiaaarodriguezz17@gmail.com</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Sofia Rodriguez</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" s="2" t="n">
-        <v>45676</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>46049</v>
-      </c>
-      <c r="G159" t="n">
-        <v>373</v>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>EMAIL_solvaldez_25@hotmail.com</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Sol Valdez</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" s="2" t="n">
-        <v>45986</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G160" t="n">
-        <v>70</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>EMAIL_stella.fernandez073@gmail.com</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Stella Fernandez</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>46063</v>
-      </c>
-      <c r="G161" t="n">
-        <v>131</v>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>EMAIL_tsvictoriavallejo@gmail.com</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="n">
-        <v>2</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>45980</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>45989</v>
-      </c>
-      <c r="G162" t="n">
-        <v>9</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>4.0 -&gt; 4.0</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>EMAIL_valeraquel79@gimail.com</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Valeria Raquel Pastrana</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" s="2" t="n">
-        <v>45922</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>46041</v>
-      </c>
-      <c r="G163" t="n">
-        <v>119</v>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>EMAIL_vanevergara21@hotmail.com</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Vanesa Vergara</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G164" t="n">
-        <v>381</v>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>EMAIL_veronicapaniga.6@gmail.com</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Verónica</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" s="2" t="n">
-        <v>45629</v>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="G165" t="n">
-        <v>377</v>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>EMAIL_victorjoseruiz443@gmail.com</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Jose Jose Jose</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" s="2" t="n">
-        <v>45671</v>
-      </c>
-      <c r="F166" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G166" t="n">
-        <v>337</v>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>EMAIL_vivu2701@gmail.com</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Ivana perez</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>46059</v>
-      </c>
-      <c r="F167" s="2" t="n">
-        <v>46020</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>EMAIL_ydatri@gmail.com</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Ye</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E168" s="2" t="n">
-        <v>45963</v>
-      </c>
-      <c r="F168" s="2" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G168" t="n">
-        <v>93</v>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>EMAIL_yuyutrr@hotmail.com</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Rosana</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="n">
-        <v>1</v>
-      </c>
-      <c r="E169" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="F169" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="G169" t="n">
-        <v>379</v>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/marketing_report/outputs/Posgrados/Otros_Reportes/reporte_journey_tiempos.xlsx
+++ b/marketing_report/outputs/Posgrados/Otros_Reportes/reporte_journey_tiempos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="331">
   <si>
     <t>Persona_ID</t>
   </si>
@@ -142,12 +142,18 @@
     <t>DNI_37105548.0</t>
   </si>
   <si>
+    <t>DNI_37729574.0</t>
+  </si>
+  <si>
     <t>DNI_38032739.0</t>
   </si>
   <si>
     <t>DNI_38035015.0</t>
   </si>
   <si>
+    <t>DNI_38184239.0</t>
+  </si>
+  <si>
     <t>DNI_38738650.0</t>
   </si>
   <si>
@@ -196,12 +202,18 @@
     <t>EMAIL_alejandrafabian53@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_aleyis@hotmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_anabmx@hotmail.com</t>
   </si>
   <si>
     <t>EMAIL_antonellatoloza05@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_ayelen.romano05@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_barloquimari@gmail.com</t>
   </si>
   <si>
@@ -211,6 +223,12 @@
     <t>EMAIL_carinavillalva@hotmail.com.ar</t>
   </si>
   <si>
+    <t>EMAIL_carocrapanzano@gmail.com</t>
+  </si>
+  <si>
+    <t>EMAIL_cecilia.0304@hotmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_cesar3.arevalo@gmail.com</t>
   </si>
   <si>
@@ -232,6 +250,9 @@
     <t>EMAIL_daiferperez89@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_daihanafernfhandez@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_danielalorena751@hotmail.com</t>
   </si>
   <si>
@@ -244,6 +265,9 @@
     <t>EMAIL_elizabethz3016@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_emanuel.ferber@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_emilopez1985@hotmail.com</t>
   </si>
   <si>
@@ -256,18 +280,21 @@
     <t>EMAIL_florcalabrese@hotmail.com</t>
   </si>
   <si>
-    <t>EMAIL_florenciamariel02@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_florzapatiel13@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_francomarcucci544@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_francomiranda297@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_frovastefano@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_gabriel3476demonio@hotmail.com.ar</t>
+  </si>
+  <si>
     <t>EMAIL_gaby.acchurallanos@hotmail.com</t>
   </si>
   <si>
@@ -289,12 +316,18 @@
     <t>EMAIL_jorgelinap300@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_judit_026@hotmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_julimaol@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_karitofierro78@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_kinemartu@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_lauraesposto@hotmail.com</t>
   </si>
   <si>
@@ -307,15 +340,24 @@
     <t>EMAIL_luuciazambrano@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_marcelokoleff10@outlook.com</t>
+  </si>
+  <si>
     <t>EMAIL_marceteje1304@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_marialaura.carrizo06@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_marialaurabuono@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_maricelcayata@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_marisarodriguez244@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_mariselguerrero3@gmail.com</t>
   </si>
   <si>
@@ -334,6 +376,9 @@
     <t>EMAIL_micaelalotufo@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_mjfsolan@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_nadita_27@hotmail.com.ar</t>
   </si>
   <si>
@@ -349,6 +394,9 @@
     <t>EMAIL_nelsonrubenpereira1327@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_nicolasbarreiro10@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_noali_84@hotmail.com</t>
   </si>
   <si>
@@ -427,9 +475,15 @@
     <t>EMAIL_verocompe@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_victorjoseruiz443@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_vidalmarcela388@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_vm.elias@hotmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_ydatri@gmail.com</t>
   </si>
   <si>
@@ -448,336 +502,384 @@
     <t>Luciana</t>
   </si>
   <si>
+    <t>GABRIELA SILVANA</t>
+  </si>
+  <si>
+    <t>ANDREA VIVIANA</t>
+  </si>
+  <si>
+    <t>Gladis</t>
+  </si>
+  <si>
+    <t>pamela reyes alonso</t>
+  </si>
+  <si>
+    <t>Rodrigo Daniel</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>carolina ortiz</t>
+  </si>
+  <si>
+    <t>Lucio Gabriel</t>
+  </si>
+  <si>
+    <t>María soledad</t>
+  </si>
+  <si>
+    <t>Miguel Pereyra</t>
+  </si>
+  <si>
+    <t>LUCAS GABRIEL</t>
+  </si>
+  <si>
+    <t>Elias Santiago</t>
+  </si>
+  <si>
+    <t>Maria Belen</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>Dana Macarena</t>
+  </si>
+  <si>
+    <t>Mercedes Soledad</t>
+  </si>
+  <si>
+    <t>Sabrina</t>
+  </si>
+  <si>
+    <t>Anahí Rebeca</t>
+  </si>
+  <si>
+    <t>Fernando Ezequiel</t>
+  </si>
+  <si>
+    <t>Yamila</t>
+  </si>
+  <si>
+    <t>VICTORIA</t>
+  </si>
+  <si>
+    <t>Pablo Alejandro</t>
+  </si>
+  <si>
+    <t>Marcela  Alejandra</t>
+  </si>
+  <si>
+    <t>Flavia Fernanda</t>
+  </si>
+  <si>
+    <t>Florencia Mariel</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>GABRIELA BEATRIZ</t>
+  </si>
+  <si>
+    <t>Maria Julieta</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>Florencia</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>Camila Florencia</t>
+  </si>
+  <si>
+    <t>Lucas Freytes de los Rios</t>
+  </si>
+  <si>
+    <t>Melanie Antonella</t>
+  </si>
+  <si>
+    <t>Yanci</t>
+  </si>
+  <si>
+    <t>FACUNDO SANTIAGO</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>Noem</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>Ale cesar</t>
+  </si>
+  <si>
+    <t>Milagros Agustina</t>
+  </si>
+  <si>
+    <t>Lucia Lucia</t>
+  </si>
+  <si>
+    <t>Alejandro Alejandro</t>
+  </si>
+  <si>
+    <t>Anita Heredia</t>
+  </si>
+  <si>
+    <t>ANTONELLA</t>
+  </si>
+  <si>
+    <t>Ayelen Sabrina Romano</t>
+  </si>
+  <si>
+    <t>Maria victoria</t>
+  </si>
+  <si>
+    <t>Angel Bartolini</t>
+  </si>
+  <si>
+    <t>Caru Villalva</t>
+  </si>
+  <si>
+    <t>Carolina Crapanzano</t>
+  </si>
+  <si>
+    <t>Cecilia Cecilia</t>
+  </si>
+  <si>
+    <t>Arevalo Cesar</t>
+  </si>
+  <si>
+    <t>CESAR A</t>
+  </si>
+  <si>
+    <t>Luciano Chiaramonte de Clermont</t>
+  </si>
+  <si>
+    <t>Claudio Fabian Arancibia</t>
+  </si>
+  <si>
+    <t>Adriana Rueda</t>
+  </si>
+  <si>
+    <t>Cristian Emanuel Lopez</t>
+  </si>
+  <si>
+    <t>Daisi Fernanda Perez</t>
+  </si>
+  <si>
+    <t>Fernandez Fernandez</t>
+  </si>
+  <si>
+    <t>Dani Martinez</t>
+  </si>
+  <si>
+    <t>DARIO</t>
+  </si>
+  <si>
+    <t>Elias</t>
+  </si>
+  <si>
+    <t>Valeria</t>
+  </si>
+  <si>
+    <t>Emanuel Ferrari</t>
+  </si>
+  <si>
+    <t>Emi Lopez</t>
+  </si>
+  <si>
+    <t>MATÍAS EZEQUIEL</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Flori</t>
+  </si>
+  <si>
+    <t>Florencia Alejandra</t>
+  </si>
+  <si>
+    <t>Franco Franco</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>Stefano Frova</t>
+  </si>
+  <si>
+    <t>Enrique Enrique Enrique</t>
+  </si>
+  <si>
+    <t>Gabriela Acchura Llanos</t>
+  </si>
+  <si>
+    <t>Georgina</t>
+  </si>
+  <si>
+    <t>giuliana antonella</t>
+  </si>
+  <si>
+    <t>Susana Susana</t>
+  </si>
+  <si>
+    <t>Celeste Rodriguez Simon</t>
+  </si>
+  <si>
+    <t>Mejorge</t>
+  </si>
+  <si>
+    <t>Jorgelina</t>
+  </si>
+  <si>
+    <t>Veronica Veronica</t>
+  </si>
+  <si>
+    <t>Ian</t>
+  </si>
+  <si>
+    <t>Carolina Mercedes</t>
+  </si>
+  <si>
+    <t>Martina Portella</t>
+  </si>
+  <si>
+    <t>Laura Esposto</t>
+  </si>
+  <si>
+    <t>Carina leiva</t>
+  </si>
+  <si>
+    <t>Luu Zambrano</t>
+  </si>
+  <si>
+    <t>Marcelo Marcelo</t>
+  </si>
+  <si>
+    <t>Marcela Alejandra Tejerina</t>
+  </si>
+  <si>
+    <t>Maria Laura Carrizo</t>
+  </si>
+  <si>
+    <t>Maria Laura</t>
+  </si>
+  <si>
+    <t>Maricel</t>
+  </si>
+  <si>
+    <t>Guerrero Cabezas Marisel</t>
+  </si>
+  <si>
+    <t>Mati Orellana</t>
+  </si>
+  <si>
+    <t>MAURO FEDERICO</t>
+  </si>
+  <si>
+    <t>Anto</t>
+  </si>
+  <si>
+    <t>nolasco meliza</t>
+  </si>
+  <si>
+    <t>Micaela Lotufo Haddad</t>
+  </si>
+  <si>
+    <t>Mario Mario Mario</t>
+  </si>
+  <si>
+    <t>Nadia Garcia</t>
+  </si>
+  <si>
+    <t>Natalia Natalia</t>
+  </si>
+  <si>
+    <t>Claudio lucas primero</t>
+  </si>
+  <si>
+    <t>Natalia Erika Schmid</t>
+  </si>
+  <si>
+    <t>Nicolas Nicolas</t>
+  </si>
+  <si>
+    <t>Noali Elisabeth Garcia</t>
+  </si>
+  <si>
+    <t>Noelia Ruiz</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>Pablo Pablo Ortiz</t>
+  </si>
+  <si>
+    <t>Pao Rey</t>
+  </si>
+  <si>
+    <t>Auchana Pau</t>
+  </si>
+  <si>
+    <t>Macarena Rodriguez</t>
+  </si>
+  <si>
+    <t>Pamela Vuistaz</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>Yamila Retamar</t>
+  </si>
+  <si>
+    <t>Ly</t>
+  </si>
+  <si>
+    <t>Daniela Reynaga</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>Rocio Pelaez</t>
+  </si>
+  <si>
+    <t>Alejandro Ra</t>
+  </si>
+  <si>
+    <t>LAURA NATALIA</t>
+  </si>
+  <si>
+    <t>Romi B Banega</t>
+  </si>
+  <si>
+    <t>Romina Sanchez</t>
+  </si>
+  <si>
+    <t>Rosa del carmen</t>
+  </si>
+  <si>
     <t>GABRIELA</t>
   </si>
   <si>
-    <t>ANDREA VIVIANA</t>
-  </si>
-  <si>
-    <t>Gladis</t>
-  </si>
-  <si>
-    <t>pamela reyes alonso</t>
-  </si>
-  <si>
-    <t>Rodrigo Daniel</t>
-  </si>
-  <si>
-    <t>Marco</t>
-  </si>
-  <si>
-    <t>carolina ortiz</t>
-  </si>
-  <si>
-    <t>Lucio Gabriel</t>
-  </si>
-  <si>
-    <t>María soledad</t>
-  </si>
-  <si>
-    <t>Miguel Pereyra</t>
-  </si>
-  <si>
-    <t>LUCAS GABRIEL</t>
-  </si>
-  <si>
-    <t>Elias Santiago</t>
-  </si>
-  <si>
-    <t>Maria Belen</t>
-  </si>
-  <si>
-    <t>Carlos</t>
-  </si>
-  <si>
-    <t>Leonardo</t>
-  </si>
-  <si>
-    <t>Dana Macarena</t>
-  </si>
-  <si>
-    <t>Mercedes Soledad</t>
-  </si>
-  <si>
-    <t>Sabrina</t>
-  </si>
-  <si>
-    <t>Anahí Rebeca</t>
-  </si>
-  <si>
-    <t>Fernando Ezequiel</t>
-  </si>
-  <si>
-    <t>Yamila</t>
-  </si>
-  <si>
-    <t>VICTORIA</t>
-  </si>
-  <si>
-    <t>Pablo Alejandro</t>
-  </si>
-  <si>
-    <t>Marcela  Alejandra</t>
-  </si>
-  <si>
-    <t>Flavia Fernanda</t>
-  </si>
-  <si>
-    <t>Sofia</t>
-  </si>
-  <si>
-    <t>GABRIELA BEATRIZ</t>
-  </si>
-  <si>
-    <t>Mariana</t>
-  </si>
-  <si>
-    <t>Florencia</t>
-  </si>
-  <si>
-    <t>German</t>
-  </si>
-  <si>
-    <t>Camila Florencia</t>
-  </si>
-  <si>
-    <t>Lucas Freytes de los Rios</t>
-  </si>
-  <si>
-    <t>Melanie Antonella</t>
-  </si>
-  <si>
-    <t>Yanci</t>
-  </si>
-  <si>
-    <t>FACUNDO SANTIAGO</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>Paola</t>
-  </si>
-  <si>
-    <t>Noem</t>
-  </si>
-  <si>
-    <t>Sonia</t>
-  </si>
-  <si>
-    <t>Ale cesar</t>
-  </si>
-  <si>
-    <t>Milagros Agustina</t>
-  </si>
-  <si>
-    <t>Lucia Lucia</t>
-  </si>
-  <si>
-    <t>Anita Heredia</t>
-  </si>
-  <si>
-    <t>ANTONELLA</t>
-  </si>
-  <si>
-    <t>Maria victoria</t>
-  </si>
-  <si>
-    <t>Angel Bartolini</t>
-  </si>
-  <si>
-    <t>Caru Villalva</t>
-  </si>
-  <si>
-    <t>Arevalo Cesar</t>
-  </si>
-  <si>
-    <t>CESAR A</t>
-  </si>
-  <si>
-    <t>Luciano Chiaramonte de Clermont</t>
-  </si>
-  <si>
-    <t>Claudio Fabian Arancibia</t>
-  </si>
-  <si>
-    <t>Adriana Rueda</t>
-  </si>
-  <si>
-    <t>Cristian Emanuel Lopez</t>
-  </si>
-  <si>
-    <t>Daisi Fernanda Perez</t>
-  </si>
-  <si>
-    <t>Dani Martinez</t>
-  </si>
-  <si>
-    <t>DARIO</t>
-  </si>
-  <si>
-    <t>Elias</t>
-  </si>
-  <si>
-    <t>Valeria</t>
-  </si>
-  <si>
-    <t>Emi Lopez</t>
-  </si>
-  <si>
-    <t>MATÍAS EZEQUIEL</t>
-  </si>
-  <si>
-    <t>Francisco</t>
-  </si>
-  <si>
-    <t>Flori</t>
-  </si>
-  <si>
-    <t>Florencia mariel</t>
-  </si>
-  <si>
-    <t>Florencia Alejandra</t>
-  </si>
-  <si>
-    <t>Franco</t>
-  </si>
-  <si>
-    <t>Stefano Frova</t>
-  </si>
-  <si>
-    <t>Gabriela Acchura Llanos</t>
-  </si>
-  <si>
-    <t>Georgina</t>
-  </si>
-  <si>
-    <t>giuliana antonella</t>
-  </si>
-  <si>
-    <t>Susana Susana</t>
-  </si>
-  <si>
-    <t>Celeste Rodriguez Simon</t>
-  </si>
-  <si>
-    <t>Mejorge</t>
-  </si>
-  <si>
-    <t>Jorgelina</t>
-  </si>
-  <si>
-    <t>Ian</t>
-  </si>
-  <si>
-    <t>Carolina Mercedes</t>
-  </si>
-  <si>
-    <t>Laura Esposto</t>
-  </si>
-  <si>
-    <t>Carina leiva</t>
-  </si>
-  <si>
-    <t>Luu Zambrano</t>
-  </si>
-  <si>
-    <t>Marcela Alejandra Tejerina</t>
-  </si>
-  <si>
-    <t>Maria Laura</t>
-  </si>
-  <si>
-    <t>Maricel</t>
-  </si>
-  <si>
-    <t>Guerrero Cabezas Marisel</t>
-  </si>
-  <si>
-    <t>Mati Orellana</t>
-  </si>
-  <si>
-    <t>MAURO FEDERICO</t>
-  </si>
-  <si>
-    <t>Anto</t>
-  </si>
-  <si>
-    <t>nolasco meliza</t>
-  </si>
-  <si>
-    <t>Micaela Lotufo Haddad</t>
-  </si>
-  <si>
-    <t>Nadia Garcia</t>
-  </si>
-  <si>
-    <t>Natalia Natalia</t>
-  </si>
-  <si>
-    <t>Claudio lucas primero</t>
-  </si>
-  <si>
-    <t>Natalia Erika Schmid</t>
-  </si>
-  <si>
-    <t>Noali Elisabeth Garcia</t>
-  </si>
-  <si>
-    <t>Noelia Ruiz</t>
-  </si>
-  <si>
-    <t>Pablo</t>
-  </si>
-  <si>
-    <t>Pablo Pablo Ortiz</t>
-  </si>
-  <si>
-    <t>Pao Rey</t>
-  </si>
-  <si>
-    <t>Auchana Pau</t>
-  </si>
-  <si>
-    <t>Macarena Rodriguez</t>
-  </si>
-  <si>
-    <t>Pamela Vuistaz</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>Yamila Retamar</t>
-  </si>
-  <si>
-    <t>Ly</t>
-  </si>
-  <si>
-    <t>Daniela Reynaga</t>
-  </si>
-  <si>
-    <t>Roberto</t>
-  </si>
-  <si>
-    <t>Rocio Pelaez</t>
-  </si>
-  <si>
-    <t>Alejandro Ra</t>
-  </si>
-  <si>
-    <t>LAURA NATALIA</t>
-  </si>
-  <si>
-    <t>Romi B Banega</t>
-  </si>
-  <si>
-    <t>Romina Sanchez</t>
-  </si>
-  <si>
-    <t>Rosa del carmen</t>
-  </si>
-  <si>
     <t>Sol Valdez</t>
   </si>
   <si>
@@ -796,18 +898,21 @@
     <t>VERONICA</t>
   </si>
   <si>
+    <t>Jose Jose Jose</t>
+  </si>
+  <si>
     <t>Marcela Alejandra</t>
   </si>
   <si>
     <t>Ye</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>18.0</t>
   </si>
   <si>
@@ -823,10 +928,10 @@
     <t>3.0 -&gt; 477.0</t>
   </si>
   <si>
-    <t>18.0 -&gt; 3.0</t>
-  </si>
-  <si>
-    <t>907.0 -&gt; 37.0 -&gt; 37.0</t>
+    <t>3.0 -&gt; 18.0</t>
+  </si>
+  <si>
+    <t>37.0 -&gt; 37.0 -&gt; 907.0</t>
   </si>
   <si>
     <t>18.0 -&gt; 18.0 -&gt; 18.0</t>
@@ -850,6 +955,9 @@
     <t>6.0</t>
   </si>
   <si>
+    <t>394.0</t>
+  </si>
+  <si>
     <t>18.0 -&gt; 18.0</t>
   </si>
   <si>
@@ -865,13 +973,13 @@
     <t>907.0</t>
   </si>
   <si>
-    <t>3.0 -&gt; 18.0</t>
-  </si>
-  <si>
     <t>27.0</t>
   </si>
   <si>
-    <t>18.0 -&gt; 18.0 -&gt; 18.0 -&gt; 18.0</t>
+    <t>18.0 -&gt; 4.0</t>
+  </si>
+  <si>
+    <t>18.0 -&gt; 18.0 -&gt; 18.0 -&gt; 18.0 -&gt; 18.0</t>
   </si>
   <si>
     <t>625.0</t>
@@ -883,6 +991,9 @@
     <t>4.0 -&gt; 4.0</t>
   </si>
   <si>
+    <t>37.0</t>
+  </si>
+  <si>
     <t>908.0</t>
   </si>
   <si>
@@ -890,9 +1001,6 @@
   </si>
   <si>
     <t>477.0</t>
-  </si>
-  <si>
-    <t>37.0</t>
   </si>
   <si>
     <t>443.0</t>
@@ -1260,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1306,7 +1414,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="C2">
         <v>17940368</v>
@@ -1320,23 +1428,20 @@
       <c r="F2" s="2">
         <v>46001</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J2" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K2" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L2" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1344,7 +1449,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C3">
         <v>2120618</v>
@@ -1358,20 +1463,23 @@
       <c r="F3" s="2">
         <v>46052</v>
       </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
       <c r="H3" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I3" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J3" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K3" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L3" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1379,7 +1487,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C4">
         <v>2181822</v>
@@ -1393,20 +1501,23 @@
       <c r="F4" s="2">
         <v>46052</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
       <c r="H4" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I4" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J4" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K4" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L4" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1414,7 +1525,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C5">
         <v>2242819</v>
@@ -1428,20 +1539,23 @@
       <c r="F5" s="2">
         <v>46052</v>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
       <c r="H5" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I5" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J5" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K5" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L5" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1449,7 +1563,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C6">
         <v>2264822</v>
@@ -1463,20 +1577,23 @@
       <c r="F6" s="2">
         <v>46052</v>
       </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
       <c r="H6" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I6" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J6" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K6" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L6" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1484,7 +1601,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C7">
         <v>22946409</v>
@@ -1493,25 +1610,28 @@
         <v>2</v>
       </c>
       <c r="E7" s="2">
-        <v>45890</v>
+        <v>45659</v>
       </c>
       <c r="F7" s="2">
         <v>46007</v>
       </c>
+      <c r="G7">
+        <v>348</v>
+      </c>
       <c r="H7" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I7" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="J7" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K7" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="L7" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1519,7 +1639,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C8">
         <v>24790890</v>
@@ -1533,20 +1653,23 @@
       <c r="F8" s="2">
         <v>45961</v>
       </c>
+      <c r="G8">
+        <v>95</v>
+      </c>
       <c r="H8" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I8" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="J8" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K8" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="L8" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1554,7 +1677,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C9">
         <v>25009560</v>
@@ -1562,23 +1685,29 @@
       <c r="D9">
         <v>2</v>
       </c>
+      <c r="E9" s="2">
+        <v>45909</v>
+      </c>
       <c r="F9" s="2">
         <v>46001</v>
       </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
       <c r="H9" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I9" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="J9" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K9" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="L9" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1586,7 +1715,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C10">
         <v>25118778</v>
@@ -1595,25 +1724,28 @@
         <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>45826</v>
+        <v>45634</v>
       </c>
       <c r="F10" s="2">
         <v>45989</v>
       </c>
+      <c r="G10">
+        <v>355</v>
+      </c>
       <c r="H10" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I10" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="J10" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K10" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="L10" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1621,7 +1753,7 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C11">
         <v>25457311</v>
@@ -1635,20 +1767,23 @@
       <c r="F11" s="2">
         <v>46056</v>
       </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
       <c r="H11" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I11" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J11" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K11" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L11" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1656,7 +1791,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C12">
         <v>26057054</v>
@@ -1665,25 +1800,28 @@
         <v>3</v>
       </c>
       <c r="E12" s="2">
-        <v>46029</v>
+        <v>45656</v>
       </c>
       <c r="F12" s="2">
         <v>46052</v>
       </c>
+      <c r="G12">
+        <v>396</v>
+      </c>
       <c r="H12" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I12" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="J12" t="s">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="K12" t="s">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="L12" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1691,7 +1829,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C13">
         <v>26131584</v>
@@ -1699,23 +1837,29 @@
       <c r="D13">
         <v>3</v>
       </c>
+      <c r="E13" s="2">
+        <v>45649</v>
+      </c>
       <c r="F13" s="2">
         <v>46017</v>
       </c>
+      <c r="G13">
+        <v>368</v>
+      </c>
       <c r="H13" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I13" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="J13" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K13" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="L13" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1723,7 +1867,7 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C14">
         <v>26936108</v>
@@ -1737,20 +1881,23 @@
       <c r="F14" s="2">
         <v>46056</v>
       </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
       <c r="H14" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I14" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J14" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K14" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L14" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1758,7 +1905,7 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C15">
         <v>28566147</v>
@@ -1772,23 +1919,20 @@
       <c r="F15" s="2">
         <v>46030</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I15" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J15" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K15" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L15" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1796,7 +1940,7 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C16">
         <v>29336116</v>
@@ -1810,20 +1954,23 @@
       <c r="F16" s="2">
         <v>46029</v>
       </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
       <c r="H16" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I16" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="J16" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="K16" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="L16" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1831,7 +1978,7 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C17">
         <v>30103833</v>
@@ -1845,23 +1992,20 @@
       <c r="F17" s="2">
         <v>45989</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I17" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="J17" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="K17" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L17" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1869,7 +2013,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="C18">
         <v>30348383</v>
@@ -1883,20 +2027,23 @@
       <c r="F18" s="2">
         <v>46056</v>
       </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
       <c r="H18" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I18" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="J18" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K18" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="L18" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1904,7 +2051,7 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C19">
         <v>30766482</v>
@@ -1918,20 +2065,23 @@
       <c r="F19" s="2">
         <v>46052</v>
       </c>
+      <c r="G19">
+        <v>29</v>
+      </c>
       <c r="H19" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I19" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="J19" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K19" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="L19" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1939,7 +2089,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C20">
         <v>30806219</v>
@@ -1947,23 +2097,29 @@
       <c r="D20">
         <v>1</v>
       </c>
+      <c r="E20" s="2">
+        <v>45681</v>
+      </c>
       <c r="F20" s="2">
         <v>46056</v>
       </c>
+      <c r="G20">
+        <v>375</v>
+      </c>
       <c r="H20" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I20" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="J20" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="K20" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L20" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1971,7 +2127,7 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C21">
         <v>31788443</v>
@@ -1985,20 +2141,23 @@
       <c r="F21" s="2">
         <v>45991</v>
       </c>
+      <c r="G21">
+        <v>160</v>
+      </c>
       <c r="H21" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I21" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J21" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K21" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L21" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2006,7 +2165,7 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C22">
         <v>31949090</v>
@@ -2020,20 +2179,23 @@
       <c r="F22" s="2">
         <v>46044</v>
       </c>
+      <c r="G22">
+        <v>294</v>
+      </c>
       <c r="H22" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I22" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J22" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K22" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L22" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2041,7 +2203,7 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C23">
         <v>32534579</v>
@@ -2049,23 +2211,26 @@
       <c r="D23">
         <v>1</v>
       </c>
+      <c r="E23" s="2">
+        <v>45659</v>
+      </c>
       <c r="F23" s="2">
         <v>46013</v>
       </c>
       <c r="H23" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I23" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="J23" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="K23" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L23" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2073,7 +2238,7 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C24">
         <v>32914047</v>
@@ -2087,20 +2252,23 @@
       <c r="F24" s="2">
         <v>46056</v>
       </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
       <c r="H24" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I24" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J24" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K24" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L24" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2108,7 +2276,7 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C25">
         <v>33753144</v>
@@ -2116,23 +2284,29 @@
       <c r="D25">
         <v>1</v>
       </c>
+      <c r="E25" s="2">
+        <v>45639</v>
+      </c>
       <c r="F25" s="2">
         <v>46024</v>
       </c>
+      <c r="G25">
+        <v>385</v>
+      </c>
       <c r="H25" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I25" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="J25" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="K25" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L25" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2140,7 +2314,7 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C26">
         <v>34524241</v>
@@ -2148,23 +2322,29 @@
       <c r="D26">
         <v>3</v>
       </c>
+      <c r="E26" s="2">
+        <v>45634</v>
+      </c>
       <c r="F26" s="2">
         <v>46058</v>
       </c>
+      <c r="G26">
+        <v>424</v>
+      </c>
       <c r="H26" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I26" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="J26" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="K26" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="L26" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2172,7 +2352,7 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C27">
         <v>35482130</v>
@@ -2180,23 +2360,29 @@
       <c r="D27">
         <v>1</v>
       </c>
+      <c r="E27" s="2">
+        <v>45652</v>
+      </c>
       <c r="F27" s="2">
         <v>46059</v>
       </c>
+      <c r="G27">
+        <v>407</v>
+      </c>
       <c r="H27" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I27" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="J27" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="K27" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L27" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2204,7 +2390,7 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="C28">
         <v>35599473</v>
@@ -2218,20 +2404,23 @@
       <c r="F28" s="2">
         <v>46056</v>
       </c>
+      <c r="G28">
+        <v>7</v>
+      </c>
       <c r="H28" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I28" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="J28" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="K28" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L28" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2239,7 +2428,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="C29">
         <v>36345824</v>
@@ -2247,23 +2436,29 @@
       <c r="D29">
         <v>1</v>
       </c>
+      <c r="E29" s="2">
+        <v>45985</v>
+      </c>
       <c r="F29" s="2">
         <v>45989</v>
       </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
       <c r="H29" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I29" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J29" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K29" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L29" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2271,7 +2466,7 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C30">
         <v>36379096</v>
@@ -2285,23 +2480,20 @@
       <c r="F30" s="2">
         <v>46062</v>
       </c>
-      <c r="G30">
-        <v>322</v>
-      </c>
       <c r="H30" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I30" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J30" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K30" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L30" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2309,7 +2501,7 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="C31">
         <v>37105548</v>
@@ -2323,23 +2515,20 @@
       <c r="F31" s="2">
         <v>46053</v>
       </c>
-      <c r="G31">
-        <v>237</v>
-      </c>
       <c r="H31" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I31" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="J31" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="K31" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L31" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2347,31 +2536,37 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C32">
-        <v>38032739</v>
+        <v>37729574</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45995</v>
       </c>
       <c r="F32" s="2">
-        <v>46009</v>
+        <v>46031</v>
+      </c>
+      <c r="G32">
+        <v>36</v>
       </c>
       <c r="H32" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I32" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="J32" t="s">
-        <v>264</v>
+        <v>313</v>
       </c>
       <c r="K32" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L32" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2379,37 +2574,37 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="C33">
-        <v>38035015</v>
+        <v>38032739</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2">
-        <v>45860</v>
+        <v>45688</v>
       </c>
       <c r="F33" s="2">
-        <v>46031</v>
+        <v>46009</v>
       </c>
       <c r="G33">
-        <v>171</v>
+        <v>321</v>
       </c>
       <c r="H33" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I33" t="s">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="J33" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K33" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L33" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2417,31 +2612,34 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C34">
-        <v>38738650</v>
+        <v>38035015</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45860</v>
       </c>
       <c r="F34" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="H34" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I34" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="J34" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="K34" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2449,34 +2647,37 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C35">
-        <v>39004179</v>
+        <v>38184239</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" s="2">
-        <v>46042</v>
+        <v>45993</v>
       </c>
       <c r="F35" s="2">
-        <v>46059</v>
+        <v>46003</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
       </c>
       <c r="H35" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I35" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J35" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K35" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L35" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2484,34 +2685,37 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C36">
-        <v>39320904</v>
+        <v>38738650</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2">
-        <v>45810</v>
+        <v>45913</v>
       </c>
       <c r="F36" s="2">
-        <v>46008</v>
+        <v>46032</v>
+      </c>
+      <c r="G36">
+        <v>119</v>
       </c>
       <c r="H36" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I36" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="J36" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K36" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2519,31 +2723,37 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="C37">
-        <v>40934003</v>
+        <v>39004179</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
+      <c r="E37" s="2">
+        <v>46042</v>
+      </c>
       <c r="F37" s="2">
-        <v>46066</v>
+        <v>46059</v>
+      </c>
+      <c r="G37">
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I37" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="J37" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="K37" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2551,31 +2761,37 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="C38">
-        <v>40934059</v>
+        <v>39320904</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
+      <c r="E38" s="2">
+        <v>45810</v>
+      </c>
       <c r="F38" s="2">
         <v>46008</v>
       </c>
+      <c r="G38">
+        <v>198</v>
+      </c>
       <c r="H38" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I38" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="J38" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K38" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="L38" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2583,31 +2799,37 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C39">
-        <v>41035709</v>
+        <v>40934003</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
+      <c r="E39" s="2">
+        <v>45911</v>
+      </c>
       <c r="F39" s="2">
-        <v>46021</v>
+        <v>46066</v>
+      </c>
+      <c r="G39">
+        <v>155</v>
       </c>
       <c r="H39" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I39" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="J39" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="K39" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2615,34 +2837,37 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C40">
-        <v>44327105</v>
+        <v>40934059</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2">
-        <v>45819</v>
+        <v>45987</v>
       </c>
       <c r="F40" s="2">
-        <v>46006</v>
+        <v>46008</v>
+      </c>
+      <c r="G40">
+        <v>21</v>
       </c>
       <c r="H40" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I40" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="J40" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="K40" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="L40" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2650,31 +2875,37 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="C41">
-        <v>44744527</v>
+        <v>41035709</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
+      <c r="E41" s="2">
+        <v>45929</v>
+      </c>
       <c r="F41" s="2">
-        <v>45992</v>
+        <v>46021</v>
+      </c>
+      <c r="G41">
+        <v>92</v>
       </c>
       <c r="H41" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I41" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="J41" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="K41" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L41" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2682,34 +2913,37 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="C42">
-        <v>4518359</v>
+        <v>44327105</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" s="2">
-        <v>46080</v>
+        <v>45819</v>
       </c>
       <c r="F42" s="2">
-        <v>46052</v>
+        <v>46006</v>
+      </c>
+      <c r="G42">
+        <v>187</v>
       </c>
       <c r="H42" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I42" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="J42" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="K42" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L42" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2717,37 +2951,34 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C43">
-        <v>45849671</v>
+        <v>44744527</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" s="2">
-        <v>45870</v>
+        <v>45629</v>
       </c>
       <c r="F43" s="2">
-        <v>46027</v>
-      </c>
-      <c r="G43">
-        <v>157</v>
+        <v>45992</v>
       </c>
       <c r="H43" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I43" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="J43" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="K43" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L43" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2755,34 +2986,37 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C44">
-        <v>4658448</v>
+        <v>4518359</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" s="2">
-        <v>46074</v>
+        <v>46080</v>
       </c>
       <c r="F44" s="2">
         <v>46052</v>
       </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
       <c r="H44" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I44" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J44" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K44" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L44" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2790,34 +3024,34 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C45">
-        <v>4869437</v>
+        <v>45849671</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" s="2">
-        <v>46081</v>
+        <v>45870</v>
       </c>
       <c r="F45" s="2">
-        <v>46052</v>
+        <v>46027</v>
       </c>
       <c r="H45" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I45" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J45" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K45" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L45" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2825,34 +3059,37 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C46">
-        <v>5679726</v>
+        <v>4658448</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46" s="2">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="F46" s="2">
         <v>46052</v>
       </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
       <c r="H46" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I46" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J46" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K46" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L46" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2860,34 +3097,37 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>183</v>
+        <v>201</v>
+      </c>
+      <c r="C47">
+        <v>4869437</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47" s="2">
-        <v>46043</v>
+        <v>46081</v>
       </c>
       <c r="F47" s="2">
-        <v>46037</v>
+        <v>46052</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I47" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="J47" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K47" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L47" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2895,28 +3135,37 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>184</v>
+        <v>202</v>
+      </c>
+      <c r="C48">
+        <v>5679726</v>
       </c>
       <c r="D48">
         <v>1</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46073</v>
       </c>
       <c r="F48" s="2">
         <v>46052</v>
       </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
       <c r="H48" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I48" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="J48" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K48" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L48" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2924,34 +3173,31 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
       <c r="E49" s="2">
-        <v>45856</v>
+        <v>46043</v>
       </c>
       <c r="F49" s="2">
-        <v>46007</v>
-      </c>
-      <c r="G49">
-        <v>151</v>
+        <v>46037</v>
       </c>
       <c r="H49" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I49" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J49" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K49" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2959,34 +3205,34 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50" s="2">
-        <v>46024</v>
+        <v>45913</v>
       </c>
       <c r="F50" s="2">
-        <v>45988</v>
+        <v>46052</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="H50" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I50" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J50" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K50" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L50" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2994,31 +3240,31 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51" s="2">
-        <v>45867</v>
+        <v>45856</v>
       </c>
       <c r="F51" s="2">
-        <v>46056</v>
+        <v>46007</v>
       </c>
       <c r="H51" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I51" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="J51" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="K51" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L51" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3026,34 +3272,31 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
       <c r="E52" s="2">
-        <v>46078</v>
+        <v>45674</v>
       </c>
       <c r="F52" s="2">
-        <v>46010</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
+        <v>45996</v>
       </c>
       <c r="H52" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I52" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="J52" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="K52" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L52" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3061,31 +3304,31 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="E53" s="2">
-        <v>46073</v>
+        <v>46024</v>
       </c>
       <c r="F53" s="2">
-        <v>46056</v>
+        <v>45988</v>
       </c>
       <c r="H53" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I53" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J53" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K53" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L53" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3093,28 +3336,34 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D54">
         <v>1</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45867</v>
       </c>
       <c r="F54" s="2">
         <v>46056</v>
       </c>
+      <c r="G54">
+        <v>189</v>
+      </c>
       <c r="H54" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I54" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="J54" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="K54" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L54" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3122,28 +3371,34 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2">
+        <v>46006</v>
+      </c>
+      <c r="F55" s="2">
+        <v>46008</v>
+      </c>
+      <c r="G55">
         <v>2</v>
       </c>
-      <c r="F55" s="2">
-        <v>46009</v>
-      </c>
       <c r="H55" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I55" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="J55" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K55" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L55" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3151,31 +3406,31 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56" s="2">
-        <v>46074</v>
+        <v>46078</v>
       </c>
       <c r="F56" s="2">
-        <v>46052</v>
+        <v>46010</v>
       </c>
       <c r="H56" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I56" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J56" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K56" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L56" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3183,31 +3438,34 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57" s="2">
-        <v>45831</v>
+        <v>46073</v>
       </c>
       <c r="F57" s="2">
-        <v>46052</v>
+        <v>46056</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I57" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J57" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K57" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L57" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3215,28 +3473,34 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
+      <c r="E58" s="2">
+        <v>45652</v>
+      </c>
       <c r="F58" s="2">
-        <v>46058</v>
+        <v>46056</v>
+      </c>
+      <c r="G58">
+        <v>404</v>
       </c>
       <c r="H58" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I58" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J58" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K58" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L58" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3244,28 +3508,31 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
+      <c r="E59" s="2">
+        <v>46001</v>
+      </c>
       <c r="F59" s="2">
-        <v>46056</v>
+        <v>45995</v>
       </c>
       <c r="H59" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I59" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J59" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K59" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L59" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3273,28 +3540,31 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
+      <c r="E60" s="2">
+        <v>45637</v>
+      </c>
       <c r="F60" s="2">
-        <v>46064</v>
+        <v>46012</v>
       </c>
       <c r="H60" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I60" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J60" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K60" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L60" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3302,28 +3572,34 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
+      <c r="E61" s="2">
+        <v>45633</v>
+      </c>
       <c r="F61" s="2">
         <v>46009</v>
       </c>
+      <c r="G61">
+        <v>376</v>
+      </c>
       <c r="H61" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I61" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="J61" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K61" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="L61" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3331,28 +3607,34 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
+      <c r="E62" s="2">
+        <v>46074</v>
+      </c>
       <c r="F62" s="2">
-        <v>46031</v>
+        <v>46052</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I62" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="J62" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K62" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L62" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3360,31 +3642,34 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="2">
-        <v>45849</v>
+        <v>45831</v>
       </c>
       <c r="F63" s="2">
-        <v>46009</v>
+        <v>46052</v>
+      </c>
+      <c r="G63">
+        <v>221</v>
       </c>
       <c r="H63" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I63" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="J63" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="K63" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="L63" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3392,28 +3677,31 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
+      <c r="E64" s="2">
+        <v>45913</v>
+      </c>
       <c r="F64" s="2">
-        <v>46049</v>
+        <v>46058</v>
       </c>
       <c r="H64" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I64" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="J64" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="K64" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L64" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3421,31 +3709,34 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="2">
-        <v>46074</v>
+        <v>45904</v>
       </c>
       <c r="F65" s="2">
-        <v>46052</v>
+        <v>46056</v>
+      </c>
+      <c r="G65">
+        <v>152</v>
       </c>
       <c r="H65" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I65" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="J65" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K65" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L65" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3453,31 +3744,34 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" s="2">
-        <v>46076</v>
+        <v>45634</v>
       </c>
       <c r="F66" s="2">
-        <v>46056</v>
+        <v>46064</v>
+      </c>
+      <c r="G66">
+        <v>430</v>
       </c>
       <c r="H66" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I66" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J66" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K66" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L66" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3485,34 +3779,34 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="2">
-        <v>46033</v>
+        <v>45911</v>
       </c>
       <c r="F67" s="2">
-        <v>45991</v>
+        <v>46009</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H67" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I67" t="s">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="J67" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="K67" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L67" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3520,31 +3814,31 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2">
-        <v>46021</v>
+        <v>45849</v>
       </c>
       <c r="F68" s="2">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="H68" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I68" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="J68" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="K68" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="L68" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3552,31 +3846,34 @@
         <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69" s="2">
-        <v>45784</v>
+        <v>45925</v>
       </c>
       <c r="F69" s="2">
-        <v>46056</v>
+        <v>46031</v>
+      </c>
+      <c r="G69">
+        <v>106</v>
       </c>
       <c r="H69" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I69" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J69" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K69" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L69" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3584,34 +3881,34 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2">
-        <v>45745</v>
+        <v>45849</v>
       </c>
       <c r="F70" s="2">
-        <v>46031</v>
+        <v>46009</v>
       </c>
       <c r="G70">
-        <v>286</v>
+        <v>160</v>
       </c>
       <c r="H70" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I70" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="J70" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="K70" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="L70" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3619,34 +3916,34 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71" s="2">
-        <v>46056</v>
+        <v>45927</v>
       </c>
       <c r="F71" s="2">
-        <v>46023</v>
+        <v>46049</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H71" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I71" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="J71" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="K71" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L71" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3654,34 +3951,34 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="2">
-        <v>46037</v>
+        <v>45978</v>
       </c>
       <c r="F72" s="2">
-        <v>46029</v>
+        <v>46052</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H72" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I72" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="J72" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="K72" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L72" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3689,31 +3986,34 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="2">
-        <v>45872</v>
+        <v>46002</v>
       </c>
       <c r="F73" s="2">
-        <v>46056</v>
+        <v>46044</v>
+      </c>
+      <c r="G73">
+        <v>42</v>
       </c>
       <c r="H73" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I73" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="J73" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K73" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L73" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3721,28 +4021,34 @@
         <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
+      <c r="E74" s="2">
+        <v>46076</v>
+      </c>
       <c r="F74" s="2">
-        <v>46010</v>
+        <v>46056</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I74" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J74" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K74" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L74" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3750,34 +4056,31 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75" s="2">
-        <v>46029</v>
+        <v>46033</v>
       </c>
       <c r="F75" s="2">
-        <v>46008</v>
-      </c>
-      <c r="G75">
-        <v>0</v>
+        <v>45991</v>
       </c>
       <c r="H75" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I75" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="J75" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="K75" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L75" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3785,34 +4088,34 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="2">
-        <v>46052</v>
+        <v>46021</v>
       </c>
       <c r="F76" s="2">
-        <v>46010</v>
+        <v>46024</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H76" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I76" t="s">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="J76" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="K76" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="L76" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3820,34 +4123,34 @@
         <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
       <c r="E77" s="2">
-        <v>46023</v>
+        <v>45784</v>
       </c>
       <c r="F77" s="2">
-        <v>46064</v>
+        <v>46056</v>
       </c>
       <c r="G77">
-        <v>41</v>
+        <v>272</v>
       </c>
       <c r="H77" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I77" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J77" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K77" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L77" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3855,28 +4158,31 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
+      <c r="E78" s="2">
+        <v>46056</v>
+      </c>
       <c r="F78" s="2">
-        <v>46056</v>
+        <v>46023</v>
       </c>
       <c r="H78" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I78" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="J78" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="K78" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L78" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3884,31 +4190,31 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" s="2">
-        <v>46064</v>
+        <v>45731</v>
       </c>
       <c r="F79" s="2">
-        <v>46056</v>
+        <v>45994</v>
       </c>
       <c r="H79" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I79" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J79" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K79" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L79" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3916,31 +4222,31 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" s="2">
-        <v>46039</v>
+        <v>46037</v>
       </c>
       <c r="F80" s="2">
-        <v>46056</v>
+        <v>46029</v>
       </c>
       <c r="H80" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I80" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="J80" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="K80" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L80" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3948,28 +4254,34 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45872</v>
       </c>
       <c r="F81" s="2">
-        <v>46052</v>
+        <v>46056</v>
+      </c>
+      <c r="G81">
+        <v>184</v>
       </c>
       <c r="H81" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I81" t="s">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="J81" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K81" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L81" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3977,34 +4289,31 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82" s="2">
-        <v>45734</v>
+        <v>45831</v>
       </c>
       <c r="F82" s="2">
-        <v>45986</v>
-      </c>
-      <c r="G82">
-        <v>252</v>
+        <v>46013</v>
       </c>
       <c r="H82" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I82" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J82" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K82" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L82" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4012,34 +4321,34 @@
         <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83" s="2">
-        <v>46017</v>
+        <v>45942</v>
       </c>
       <c r="F83" s="2">
-        <v>46011</v>
+        <v>46010</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H83" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I83" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J83" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K83" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L83" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4047,57 +4356,63 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
+      <c r="E84" s="2">
+        <v>46029</v>
+      </c>
       <c r="F84" s="2">
-        <v>46052</v>
+        <v>46008</v>
       </c>
       <c r="H84" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I84" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J84" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K84" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L84" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
         <v>95</v>
       </c>
+      <c r="B85" t="s">
+        <v>239</v>
+      </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85" s="2">
-        <v>46069</v>
+        <v>46052</v>
       </c>
       <c r="F85" s="2">
-        <v>46031</v>
+        <v>46010</v>
       </c>
       <c r="H85" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I85" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="J85" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="K85" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L85" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4105,28 +4420,31 @@
         <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
+      <c r="E86" s="2">
+        <v>46023</v>
+      </c>
       <c r="F86" s="2">
-        <v>46010</v>
+        <v>46064</v>
       </c>
       <c r="H86" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I86" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J86" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K86" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L86" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4134,28 +4452,34 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
+      <c r="E87" s="2">
+        <v>45973</v>
+      </c>
       <c r="F87" s="2">
-        <v>45992</v>
+        <v>46056</v>
+      </c>
+      <c r="G87">
+        <v>83</v>
       </c>
       <c r="H87" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I87" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J87" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K87" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L87" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4163,31 +4487,34 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="D88">
         <v>1</v>
       </c>
       <c r="E88" s="2">
-        <v>45840</v>
+        <v>46064</v>
       </c>
       <c r="F88" s="2">
-        <v>46001</v>
+        <v>46056</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
       </c>
       <c r="H88" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I88" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J88" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K88" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L88" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4195,31 +4522,34 @@
         <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89" s="2">
-        <v>45864</v>
+        <v>46039</v>
       </c>
       <c r="F89" s="2">
         <v>46056</v>
       </c>
+      <c r="G89">
+        <v>17</v>
+      </c>
       <c r="H89" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I89" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="J89" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="K89" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L89" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4227,28 +4557,31 @@
         <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E90" s="2">
+        <v>46039</v>
       </c>
       <c r="F90" s="2">
-        <v>46001</v>
+        <v>45993</v>
       </c>
       <c r="H90" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I90" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="J90" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="K90" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L90" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4256,28 +4589,34 @@
         <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
+      <c r="E91" s="2">
+        <v>45660</v>
+      </c>
       <c r="F91" s="2">
-        <v>46056</v>
+        <v>46052</v>
+      </c>
+      <c r="G91">
+        <v>392</v>
       </c>
       <c r="H91" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I91" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="J91" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="K91" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L91" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4285,34 +4624,31 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" s="2">
-        <v>46057</v>
+        <v>45734</v>
       </c>
       <c r="F92" s="2">
-        <v>46009</v>
-      </c>
-      <c r="G92">
-        <v>0</v>
+        <v>45986</v>
       </c>
       <c r="H92" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I92" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="J92" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="K92" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L92" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4320,34 +4656,34 @@
         <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93" s="2">
-        <v>46071</v>
+        <v>45998</v>
       </c>
       <c r="F93" s="2">
-        <v>45986</v>
+        <v>46052</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H93" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I93" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J93" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K93" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L93" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4355,28 +4691,31 @@
         <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
+      <c r="E94" s="2">
+        <v>46017</v>
+      </c>
       <c r="F94" s="2">
-        <v>46008</v>
+        <v>46011</v>
       </c>
       <c r="H94" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I94" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J94" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K94" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L94" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4384,63 +4723,66 @@
         <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
+      <c r="E95" s="2">
+        <v>45930</v>
+      </c>
       <c r="F95" s="2">
-        <v>46044</v>
+        <v>46052</v>
+      </c>
+      <c r="G95">
+        <v>122</v>
       </c>
       <c r="H95" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I95" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J95" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K95" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L95" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
         <v>106</v>
       </c>
-      <c r="B96" t="s">
-        <v>231</v>
-      </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96" s="2">
-        <v>45872</v>
+        <v>46069</v>
       </c>
       <c r="F96" s="2">
-        <v>46050</v>
+        <v>46031</v>
       </c>
       <c r="G96">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H96" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I96" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="J96" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="K96" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L96" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4448,34 +4790,34 @@
         <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97" s="2">
-        <v>46040</v>
+        <v>45912</v>
       </c>
       <c r="F97" s="2">
-        <v>45995</v>
+        <v>46010</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H97" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I97" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J97" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K97" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L97" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4483,34 +4825,31 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98" s="2">
-        <v>46042</v>
+        <v>45973</v>
       </c>
       <c r="F98" s="2">
-        <v>45987</v>
-      </c>
-      <c r="G98">
-        <v>0</v>
+        <v>45986</v>
       </c>
       <c r="H98" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I98" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J98" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K98" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L98" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4518,63 +4857,66 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99" s="2">
-        <v>46058</v>
+        <v>45639</v>
       </c>
       <c r="F99" s="2">
-        <v>46065</v>
+        <v>45992</v>
       </c>
       <c r="G99">
-        <v>7</v>
+        <v>353</v>
       </c>
       <c r="H99" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I99" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J99" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K99" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L99" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
         <v>110</v>
       </c>
+      <c r="B100" t="s">
+        <v>253</v>
+      </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" s="2">
-        <v>46063</v>
+        <v>45996</v>
       </c>
       <c r="F100" s="2">
-        <v>45989</v>
+        <v>46007</v>
       </c>
       <c r="H100" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I100" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="J100" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="K100" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L100" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4582,28 +4924,34 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
+      <c r="E101" s="2">
+        <v>45840</v>
+      </c>
       <c r="F101" s="2">
-        <v>46000</v>
+        <v>46001</v>
+      </c>
+      <c r="G101">
+        <v>161</v>
       </c>
       <c r="H101" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I101" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J101" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K101" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L101" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4611,57 +4959,66 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45864</v>
       </c>
       <c r="F102" s="2">
-        <v>46062</v>
+        <v>46056</v>
+      </c>
+      <c r="G102">
+        <v>192</v>
       </c>
       <c r="H102" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I102" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="J102" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K102" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L102" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
         <v>113</v>
       </c>
-      <c r="B103" t="s">
-        <v>237</v>
-      </c>
       <c r="D103">
         <v>1</v>
       </c>
+      <c r="E103" s="2">
+        <v>46001</v>
+      </c>
       <c r="F103" s="2">
-        <v>46056</v>
+        <v>46065</v>
+      </c>
+      <c r="G103">
+        <v>64</v>
       </c>
       <c r="H103" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I103" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="J103" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="K103" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L103" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4669,28 +5026,34 @@
         <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45908</v>
       </c>
       <c r="F104" s="2">
-        <v>46052</v>
+        <v>46001</v>
+      </c>
+      <c r="G104">
+        <v>93</v>
       </c>
       <c r="H104" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I104" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="J104" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K104" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L104" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4698,28 +5061,34 @@
         <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
+      <c r="E105" s="2">
+        <v>45659</v>
+      </c>
       <c r="F105" s="2">
-        <v>45996</v>
+        <v>46056</v>
+      </c>
+      <c r="G105">
+        <v>397</v>
       </c>
       <c r="H105" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I105" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
       <c r="J105" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
       <c r="K105" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L105" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4727,31 +5096,31 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106" s="2">
-        <v>46027</v>
+        <v>46057</v>
       </c>
       <c r="F106" s="2">
-        <v>46052</v>
+        <v>46009</v>
       </c>
       <c r="H106" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I106" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="J106" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="K106" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L106" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4759,28 +5128,31 @@
         <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
+      <c r="E107" s="2">
+        <v>46071</v>
+      </c>
       <c r="F107" s="2">
-        <v>46052</v>
+        <v>45986</v>
       </c>
       <c r="H107" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I107" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J107" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K107" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L107" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4788,28 +5160,34 @@
         <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
+      <c r="E108" s="2">
+        <v>45984</v>
+      </c>
       <c r="F108" s="2">
-        <v>46010</v>
+        <v>46008</v>
+      </c>
+      <c r="G108">
+        <v>24</v>
       </c>
       <c r="H108" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I108" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J108" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K108" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L108" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4817,31 +5195,34 @@
         <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109" s="2">
-        <v>45821</v>
+        <v>45902</v>
       </c>
       <c r="F109" s="2">
-        <v>46052</v>
+        <v>46044</v>
+      </c>
+      <c r="G109">
+        <v>142</v>
       </c>
       <c r="H109" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I109" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="J109" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="K109" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L109" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4849,31 +5230,31 @@
         <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110" s="2">
-        <v>46039</v>
+        <v>45931</v>
       </c>
       <c r="F110" s="2">
-        <v>46056</v>
+        <v>45989</v>
       </c>
       <c r="H110" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I110" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="J110" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="K110" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L110" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4881,31 +5262,31 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="2">
-        <v>46029</v>
+        <v>45872</v>
       </c>
       <c r="F111" s="2">
-        <v>46056</v>
+        <v>46050</v>
       </c>
       <c r="H111" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I111" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="J111" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K111" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L111" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4913,28 +5294,31 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="E112" s="2">
+        <v>46040</v>
       </c>
       <c r="F112" s="2">
-        <v>46029</v>
+        <v>45995</v>
       </c>
       <c r="H112" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I112" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="J112" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K112" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L112" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -4942,31 +5326,31 @@
         <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113" s="2">
-        <v>45848</v>
+        <v>46042</v>
       </c>
       <c r="F113" s="2">
-        <v>46052</v>
+        <v>45987</v>
       </c>
       <c r="H113" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="I113" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="J113" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="K113" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L113" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -4974,57 +5358,63 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
+      <c r="E114" s="2">
+        <v>46058</v>
+      </c>
       <c r="F114" s="2">
-        <v>46003</v>
+        <v>46065</v>
       </c>
       <c r="H114" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I114" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J114" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K114" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L114" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
         <v>125</v>
       </c>
-      <c r="B115" t="s">
-        <v>249</v>
-      </c>
       <c r="D115">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E115" s="2">
+        <v>46063</v>
       </c>
       <c r="F115" s="2">
-        <v>46009</v>
+        <v>45989</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
       </c>
       <c r="H115" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I115" t="s">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="J115" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="K115" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="L115" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5032,34 +5422,31 @@
         <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116" s="2">
-        <v>46041</v>
+        <v>46050</v>
       </c>
       <c r="F116" s="2">
-        <v>46022</v>
-      </c>
-      <c r="G116">
-        <v>0</v>
+        <v>46044</v>
       </c>
       <c r="H116" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="I116" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="J116" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="K116" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L116" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5067,31 +5454,34 @@
         <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117" s="2">
-        <v>45826</v>
+        <v>45942</v>
       </c>
       <c r="F117" s="2">
-        <v>46042</v>
+        <v>46000</v>
+      </c>
+      <c r="G117">
+        <v>58</v>
       </c>
       <c r="H117" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I117" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J117" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K117" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L117" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -5099,31 +5489,34 @@
         <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="2">
-        <v>45844</v>
+        <v>45945</v>
       </c>
       <c r="F118" s="2">
-        <v>46056</v>
+        <v>46062</v>
+      </c>
+      <c r="G118">
+        <v>117</v>
       </c>
       <c r="H118" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I118" t="s">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="J118" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K118" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L118" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5131,34 +5524,34 @@
         <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119" s="2">
-        <v>46036</v>
+        <v>45935</v>
       </c>
       <c r="F119" s="2">
-        <v>46043</v>
+        <v>46056</v>
       </c>
       <c r="G119">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="H119" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I119" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="J119" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="K119" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L119" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5166,31 +5559,34 @@
         <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120" s="2">
-        <v>46058</v>
+        <v>45676</v>
       </c>
       <c r="F120" s="2">
-        <v>45978</v>
+        <v>46052</v>
+      </c>
+      <c r="G120">
+        <v>376</v>
       </c>
       <c r="H120" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I120" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="J120" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="K120" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L120" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5198,28 +5594,34 @@
         <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
+      <c r="E121" s="2">
+        <v>45960</v>
+      </c>
       <c r="F121" s="2">
-        <v>46056</v>
+        <v>45996</v>
+      </c>
+      <c r="G121">
+        <v>36</v>
       </c>
       <c r="H121" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I121" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J121" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K121" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L121" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5227,31 +5629,34 @@
         <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="2">
-        <v>46037</v>
+        <v>46026</v>
       </c>
       <c r="F122" s="2">
-        <v>46059</v>
+        <v>46052</v>
+      </c>
+      <c r="G122">
+        <v>26</v>
       </c>
       <c r="H122" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I122" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="J122" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="K122" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="L122" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5259,31 +5664,34 @@
         <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123" s="2">
-        <v>45830</v>
+        <v>45980</v>
       </c>
       <c r="F123" s="2">
         <v>46052</v>
       </c>
+      <c r="G123">
+        <v>72</v>
+      </c>
       <c r="H123" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I123" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J123" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K123" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L123" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5291,28 +5699,34 @@
         <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45913</v>
       </c>
       <c r="F124" s="2">
-        <v>45989</v>
+        <v>46010</v>
+      </c>
+      <c r="G124">
+        <v>97</v>
       </c>
       <c r="H124" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I124" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="J124" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="K124" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="L124" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5320,28 +5734,34 @@
         <v>135</v>
       </c>
       <c r="B125" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
+      <c r="E125" s="2">
+        <v>45821</v>
+      </c>
       <c r="F125" s="2">
-        <v>46041</v>
+        <v>46052</v>
+      </c>
+      <c r="G125">
+        <v>231</v>
       </c>
       <c r="H125" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="I125" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="J125" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="K125" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L125" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5349,28 +5769,34 @@
         <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
+      <c r="E126" s="2">
+        <v>46039</v>
+      </c>
       <c r="F126" s="2">
-        <v>46006</v>
+        <v>46056</v>
+      </c>
+      <c r="G126">
+        <v>17</v>
       </c>
       <c r="H126" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I126" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="J126" t="s">
-        <v>264</v>
+        <v>299</v>
       </c>
       <c r="K126" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L126" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5378,34 +5804,34 @@
         <v>137</v>
       </c>
       <c r="B127" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" s="2">
-        <v>46072</v>
+        <v>45906</v>
       </c>
       <c r="F127" s="2">
-        <v>46038</v>
+        <v>46056</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H127" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="I127" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="J127" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="K127" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L127" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5413,28 +5839,646 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45674</v>
       </c>
       <c r="F128" s="2">
+        <v>46029</v>
+      </c>
+      <c r="G128">
+        <v>355</v>
+      </c>
+      <c r="H128" t="s">
+        <v>298</v>
+      </c>
+      <c r="I128" t="s">
+        <v>321</v>
+      </c>
+      <c r="J128" t="s">
+        <v>299</v>
+      </c>
+      <c r="K128" t="s">
+        <v>299</v>
+      </c>
+      <c r="L128" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" t="s">
+        <v>139</v>
+      </c>
+      <c r="B129" t="s">
+        <v>280</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45848</v>
+      </c>
+      <c r="F129" s="2">
+        <v>46052</v>
+      </c>
+      <c r="G129">
+        <v>204</v>
+      </c>
+      <c r="H129" t="s">
+        <v>298</v>
+      </c>
+      <c r="I129" t="s">
+        <v>310</v>
+      </c>
+      <c r="J129" t="s">
+        <v>310</v>
+      </c>
+      <c r="K129" t="s">
+        <v>327</v>
+      </c>
+      <c r="L129" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" t="s">
+        <v>140</v>
+      </c>
+      <c r="B130" t="s">
+        <v>281</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45683</v>
+      </c>
+      <c r="F130" s="2">
+        <v>46003</v>
+      </c>
+      <c r="H130" t="s">
+        <v>297</v>
+      </c>
+      <c r="I130" t="s">
+        <v>299</v>
+      </c>
+      <c r="J130" t="s">
+        <v>299</v>
+      </c>
+      <c r="K130" t="s">
+        <v>327</v>
+      </c>
+      <c r="L130" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" t="s">
+        <v>141</v>
+      </c>
+      <c r="B131" t="s">
+        <v>282</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45670</v>
+      </c>
+      <c r="F131" s="2">
+        <v>46009</v>
+      </c>
+      <c r="G131">
+        <v>339</v>
+      </c>
+      <c r="H131" t="s">
+        <v>298</v>
+      </c>
+      <c r="I131" t="s">
+        <v>314</v>
+      </c>
+      <c r="J131" t="s">
+        <v>299</v>
+      </c>
+      <c r="K131" t="s">
+        <v>299</v>
+      </c>
+      <c r="L131" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" t="s">
+        <v>142</v>
+      </c>
+      <c r="B132" t="s">
+        <v>283</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132" s="2">
+        <v>46041</v>
+      </c>
+      <c r="F132" s="2">
+        <v>46022</v>
+      </c>
+      <c r="H132" t="s">
+        <v>297</v>
+      </c>
+      <c r="I132" t="s">
+        <v>310</v>
+      </c>
+      <c r="J132" t="s">
+        <v>310</v>
+      </c>
+      <c r="K132" t="s">
+        <v>327</v>
+      </c>
+      <c r="L132" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" t="s">
+        <v>143</v>
+      </c>
+      <c r="B133" t="s">
+        <v>284</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45826</v>
+      </c>
+      <c r="F133" s="2">
+        <v>46042</v>
+      </c>
+      <c r="G133">
+        <v>216</v>
+      </c>
+      <c r="H133" t="s">
+        <v>298</v>
+      </c>
+      <c r="I133" t="s">
+        <v>299</v>
+      </c>
+      <c r="J133" t="s">
+        <v>299</v>
+      </c>
+      <c r="K133" t="s">
+        <v>327</v>
+      </c>
+      <c r="L133" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" t="s">
+        <v>144</v>
+      </c>
+      <c r="B134" t="s">
+        <v>285</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45844</v>
+      </c>
+      <c r="F134" s="2">
         <v>46056</v>
       </c>
-      <c r="H128" t="s">
-        <v>263</v>
-      </c>
-      <c r="I128" t="s">
-        <v>264</v>
-      </c>
-      <c r="J128" t="s">
-        <v>264</v>
-      </c>
-      <c r="K128" t="s">
+      <c r="G134">
+        <v>212</v>
+      </c>
+      <c r="H134" t="s">
+        <v>298</v>
+      </c>
+      <c r="I134" t="s">
+        <v>299</v>
+      </c>
+      <c r="J134" t="s">
+        <v>299</v>
+      </c>
+      <c r="K134" t="s">
+        <v>327</v>
+      </c>
+      <c r="L134" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" t="s">
+        <v>145</v>
+      </c>
+      <c r="B135" t="s">
+        <v>286</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135" s="2">
+        <v>46036</v>
+      </c>
+      <c r="F135" s="2">
+        <v>46043</v>
+      </c>
+      <c r="H135" t="s">
+        <v>297</v>
+      </c>
+      <c r="I135" t="s">
+        <v>322</v>
+      </c>
+      <c r="J135" t="s">
+        <v>322</v>
+      </c>
+      <c r="K135" t="s">
+        <v>327</v>
+      </c>
+      <c r="L135" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" t="s">
+        <v>146</v>
+      </c>
+      <c r="B136" t="s">
+        <v>287</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136" s="2">
+        <v>46058</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45978</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136" t="s">
+        <v>298</v>
+      </c>
+      <c r="I136" t="s">
+        <v>323</v>
+      </c>
+      <c r="J136" t="s">
+        <v>323</v>
+      </c>
+      <c r="K136" t="s">
+        <v>327</v>
+      </c>
+      <c r="L136" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" t="s">
+        <v>147</v>
+      </c>
+      <c r="B137" t="s">
+        <v>288</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45986</v>
+      </c>
+      <c r="F137" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G137">
+        <v>70</v>
+      </c>
+      <c r="H137" t="s">
+        <v>298</v>
+      </c>
+      <c r="I137" t="s">
+        <v>299</v>
+      </c>
+      <c r="J137" t="s">
+        <v>299</v>
+      </c>
+      <c r="K137" t="s">
+        <v>327</v>
+      </c>
+      <c r="L137" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" t="s">
+        <v>148</v>
+      </c>
+      <c r="B138" t="s">
+        <v>289</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138" s="2">
+        <v>46037</v>
+      </c>
+      <c r="F138" s="2">
+        <v>46059</v>
+      </c>
+      <c r="G138">
+        <v>22</v>
+      </c>
+      <c r="H138" t="s">
+        <v>298</v>
+      </c>
+      <c r="I138" t="s">
+        <v>300</v>
+      </c>
+      <c r="J138" t="s">
+        <v>300</v>
+      </c>
+      <c r="K138" t="s">
+        <v>327</v>
+      </c>
+      <c r="L138" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" t="s">
+        <v>149</v>
+      </c>
+      <c r="B139" t="s">
         <v>290</v>
       </c>
-      <c r="L128" t="s">
-        <v>290</v>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45830</v>
+      </c>
+      <c r="F139" s="2">
+        <v>46052</v>
+      </c>
+      <c r="G139">
+        <v>222</v>
+      </c>
+      <c r="H139" t="s">
+        <v>298</v>
+      </c>
+      <c r="I139" t="s">
+        <v>299</v>
+      </c>
+      <c r="J139" t="s">
+        <v>299</v>
+      </c>
+      <c r="K139" t="s">
+        <v>327</v>
+      </c>
+      <c r="L139" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" t="s">
+        <v>150</v>
+      </c>
+      <c r="B140" t="s">
+        <v>291</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45980</v>
+      </c>
+      <c r="F140" s="2">
+        <v>45989</v>
+      </c>
+      <c r="G140">
+        <v>9</v>
+      </c>
+      <c r="H140" t="s">
+        <v>298</v>
+      </c>
+      <c r="I140" t="s">
+        <v>324</v>
+      </c>
+      <c r="J140" t="s">
+        <v>309</v>
+      </c>
+      <c r="K140" t="s">
+        <v>309</v>
+      </c>
+      <c r="L140" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141" t="s">
+        <v>151</v>
+      </c>
+      <c r="B141" t="s">
+        <v>292</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45922</v>
+      </c>
+      <c r="F141" s="2">
+        <v>46041</v>
+      </c>
+      <c r="G141">
+        <v>119</v>
+      </c>
+      <c r="H141" t="s">
+        <v>298</v>
+      </c>
+      <c r="I141" t="s">
+        <v>299</v>
+      </c>
+      <c r="J141" t="s">
+        <v>299</v>
+      </c>
+      <c r="K141" t="s">
+        <v>327</v>
+      </c>
+      <c r="L141" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142" t="s">
+        <v>152</v>
+      </c>
+      <c r="B142" t="s">
+        <v>293</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45973</v>
+      </c>
+      <c r="F142" s="2">
+        <v>46006</v>
+      </c>
+      <c r="H142" t="s">
+        <v>297</v>
+      </c>
+      <c r="I142" t="s">
+        <v>299</v>
+      </c>
+      <c r="J142" t="s">
+        <v>299</v>
+      </c>
+      <c r="K142" t="s">
+        <v>327</v>
+      </c>
+      <c r="L142" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143" t="s">
+        <v>153</v>
+      </c>
+      <c r="B143" t="s">
+        <v>294</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45671</v>
+      </c>
+      <c r="F143" s="2">
+        <v>46008</v>
+      </c>
+      <c r="H143" t="s">
+        <v>297</v>
+      </c>
+      <c r="I143" t="s">
+        <v>299</v>
+      </c>
+      <c r="J143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K143" t="s">
+        <v>327</v>
+      </c>
+      <c r="L143" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144" t="s">
+        <v>154</v>
+      </c>
+      <c r="B144" t="s">
+        <v>295</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144" s="2">
+        <v>46072</v>
+      </c>
+      <c r="F144" s="2">
+        <v>46038</v>
+      </c>
+      <c r="H144" t="s">
+        <v>297</v>
+      </c>
+      <c r="I144" t="s">
+        <v>318</v>
+      </c>
+      <c r="J144" t="s">
+        <v>318</v>
+      </c>
+      <c r="K144" t="s">
+        <v>327</v>
+      </c>
+      <c r="L144" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145" t="s">
+        <v>155</v>
+      </c>
+      <c r="B145" t="s">
+        <v>226</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45999</v>
+      </c>
+      <c r="F145" s="2">
+        <v>46002</v>
+      </c>
+      <c r="G145">
+        <v>3</v>
+      </c>
+      <c r="H145" t="s">
+        <v>298</v>
+      </c>
+      <c r="I145" t="s">
+        <v>299</v>
+      </c>
+      <c r="J145" t="s">
+        <v>299</v>
+      </c>
+      <c r="K145" t="s">
+        <v>327</v>
+      </c>
+      <c r="L145" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
+      <c r="A146" t="s">
+        <v>156</v>
+      </c>
+      <c r="B146" t="s">
+        <v>296</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45963</v>
+      </c>
+      <c r="F146" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G146">
+        <v>93</v>
+      </c>
+      <c r="H146" t="s">
+        <v>298</v>
+      </c>
+      <c r="I146" t="s">
+        <v>299</v>
+      </c>
+      <c r="J146" t="s">
+        <v>299</v>
+      </c>
+      <c r="K146" t="s">
+        <v>327</v>
+      </c>
+      <c r="L146" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Posgrados/Otros_Reportes/reporte_journey_tiempos.xlsx
+++ b/marketing_report/outputs/Posgrados/Otros_Reportes/reporte_journey_tiempos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="262">
   <si>
     <t>Persona_ID</t>
   </si>
@@ -55,18 +55,6 @@
     <t>DNI_17940368.0</t>
   </si>
   <si>
-    <t>DNI_2120618.0</t>
-  </si>
-  <si>
-    <t>DNI_2181822.0</t>
-  </si>
-  <si>
-    <t>DNI_2242819.0</t>
-  </si>
-  <si>
-    <t>DNI_2264822.0</t>
-  </si>
-  <si>
     <t>DNI_22946409.0</t>
   </si>
   <si>
@@ -79,18 +67,12 @@
     <t>DNI_25118778.0</t>
   </si>
   <si>
-    <t>DNI_25457311.0</t>
-  </si>
-  <si>
     <t>DNI_26057054.0</t>
   </si>
   <si>
     <t>DNI_26131584.0</t>
   </si>
   <si>
-    <t>DNI_26936108.0</t>
-  </si>
-  <si>
     <t>DNI_28566147.0</t>
   </si>
   <si>
@@ -100,15 +82,9 @@
     <t>DNI_30103833.0</t>
   </si>
   <si>
-    <t>DNI_30348383.0</t>
-  </si>
-  <si>
     <t>DNI_30766482.0</t>
   </si>
   <si>
-    <t>DNI_30806219.0</t>
-  </si>
-  <si>
     <t>DNI_31788443.0</t>
   </si>
   <si>
@@ -118,9 +94,6 @@
     <t>DNI_32534579.0</t>
   </si>
   <si>
-    <t>DNI_32914047.0</t>
-  </si>
-  <si>
     <t>DNI_33753144.0</t>
   </si>
   <si>
@@ -130,9 +103,6 @@
     <t>DNI_35482130.0</t>
   </si>
   <si>
-    <t>DNI_35599473.0</t>
-  </si>
-  <si>
     <t>DNI_36345824.0</t>
   </si>
   <si>
@@ -178,27 +148,15 @@
     <t>DNI_44744527.0</t>
   </si>
   <si>
-    <t>DNI_4518359.0</t>
+    <t>DNI_45771238.0</t>
   </si>
   <si>
     <t>DNI_45849671.0</t>
   </si>
   <si>
-    <t>DNI_4658448.0</t>
-  </si>
-  <si>
-    <t>DNI_4869437.0</t>
-  </si>
-  <si>
-    <t>DNI_5679726.0</t>
-  </si>
-  <si>
     <t>EMAIL_acbaires@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_agustinaliendro495@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_alejandrafabian53@gmail.com</t>
   </si>
   <si>
@@ -208,21 +166,12 @@
     <t>EMAIL_anabmx@hotmail.com</t>
   </si>
   <si>
-    <t>EMAIL_antonellatoloza05@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_ayelen.romano05@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_barloquimari@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_bartolini.david@outlook.com</t>
-  </si>
-  <si>
-    <t>EMAIL_carinavillalva@hotmail.com.ar</t>
-  </si>
-  <si>
     <t>EMAIL_carocrapanzano@gmail.com</t>
   </si>
   <si>
@@ -232,18 +181,12 @@
     <t>EMAIL_cesar3.arevalo@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_cesaraveron1@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_chiaramonteluciano@hotmail.com</t>
   </si>
   <si>
     <t>EMAIL_claufaran79@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_colqueveronica1@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_cristianlopezla12@gmail.com</t>
   </si>
   <si>
@@ -262,24 +205,15 @@
     <t>EMAIL_eliasdavidperez0@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_elizabethz3016@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_emanuel.ferber@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_emilopez1985@hotmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_ezegero24@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_fgimenez@ucasal.edu.ar</t>
   </si>
   <si>
-    <t>EMAIL_florcalabrese@hotmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_florzapatiel13@gmail.com</t>
   </si>
   <si>
@@ -289,9 +223,6 @@
     <t>EMAIL_francomiranda297@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_frovastefano@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_gabriel3476demonio@hotmail.com.ar</t>
   </si>
   <si>
@@ -307,15 +238,6 @@
     <t>EMAIL_hijoteamo375@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_hormitaki@hotmail.com</t>
-  </si>
-  <si>
-    <t>EMAIL_jorgeandresburgos82@gmail.com</t>
-  </si>
-  <si>
-    <t>EMAIL_jorgelinap300@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_judit_026@hotmail.com</t>
   </si>
   <si>
@@ -325,9 +247,6 @@
     <t>EMAIL_karitofierro78@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_kinemartu@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_lauraesposto@hotmail.com</t>
   </si>
   <si>
@@ -361,9 +280,6 @@
     <t>EMAIL_mariselguerrero3@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_matias.orellan@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_mauriv10481@yahoo.com.ar</t>
   </si>
   <si>
@@ -403,7 +319,7 @@
     <t>EMAIL_noe_abril_89@hotmail.com</t>
   </si>
   <si>
-    <t>EMAIL_pablo.larocca@gmail.com</t>
+    <t>EMAIL_ofernanda182@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_pabloortiz_ar@live.com.ar</t>
@@ -412,24 +328,12 @@
     <t>EMAIL_paorey06@live.com.ar</t>
   </si>
   <si>
-    <t>EMAIL_paulandrrea43@hotmail.com</t>
-  </si>
-  <si>
-    <t>EMAIL_psicoprofe2017@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_pvuistaz@gmail.com</t>
   </si>
   <si>
     <t>EMAIL_rajoliliana@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_retamar.yamilaa@gmail.com</t>
-  </si>
-  <si>
-    <t>EMAIL_retamozoliliana1407@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_reynagadaniela116@gmail.com</t>
   </si>
   <si>
@@ -448,18 +352,15 @@
     <t>EMAIL_romibarrios9@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_romina.sancheez@gmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_rosymiamor758@gmail.com</t>
   </si>
   <si>
+    <t>EMAIL_ruizgracielaguadalupe396518@gmail.com</t>
+  </si>
+  <si>
     <t>EMAIL_sciam740@gmail.com</t>
   </si>
   <si>
-    <t>EMAIL_solvaldez_25@hotmail.com</t>
-  </si>
-  <si>
     <t>EMAIL_tamaguilar00@gmail.com</t>
   </si>
   <si>
@@ -484,24 +385,9 @@
     <t>EMAIL_vm.elias@hotmail.com</t>
   </si>
   <si>
-    <t>EMAIL_ydatri@gmail.com</t>
-  </si>
-  <si>
     <t>NANCY BEATRIZ</t>
   </si>
   <si>
-    <t>Selva Vanesa</t>
-  </si>
-  <si>
-    <t>Viviana</t>
-  </si>
-  <si>
-    <t>Reynaldo Gaston</t>
-  </si>
-  <si>
-    <t>Luciana</t>
-  </si>
-  <si>
     <t>GABRIELA SILVANA</t>
   </si>
   <si>
@@ -514,18 +400,12 @@
     <t>pamela reyes alonso</t>
   </si>
   <si>
-    <t>Rodrigo Daniel</t>
-  </si>
-  <si>
     <t>Marco</t>
   </si>
   <si>
     <t>carolina ortiz</t>
   </si>
   <si>
-    <t>Lucio Gabriel</t>
-  </si>
-  <si>
     <t>María soledad</t>
   </si>
   <si>
@@ -535,15 +415,9 @@
     <t>LUCAS GABRIEL</t>
   </si>
   <si>
-    <t>Elias Santiago</t>
-  </si>
-  <si>
     <t>Maria Belen</t>
   </si>
   <si>
-    <t>Carlos</t>
-  </si>
-  <si>
     <t>Leonardo</t>
   </si>
   <si>
@@ -553,9 +427,6 @@
     <t>Mercedes Soledad</t>
   </si>
   <si>
-    <t>Sabrina</t>
-  </si>
-  <si>
     <t>Anahí Rebeca</t>
   </si>
   <si>
@@ -565,9 +436,6 @@
     <t>Yamila</t>
   </si>
   <si>
-    <t>VICTORIA</t>
-  </si>
-  <si>
     <t>Pablo Alejandro</t>
   </si>
   <si>
@@ -613,24 +481,12 @@
     <t>FACUNDO SANTIAGO</t>
   </si>
   <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>Paola</t>
-  </si>
-  <si>
-    <t>Noem</t>
-  </si>
-  <si>
-    <t>Sonia</t>
+    <t>CARLOS MAURICIO</t>
   </si>
   <si>
     <t>Ale cesar</t>
   </si>
   <si>
-    <t>Milagros Agustina</t>
-  </si>
-  <si>
     <t>Lucia Lucia</t>
   </si>
   <si>
@@ -640,21 +496,12 @@
     <t>Anita Heredia</t>
   </si>
   <si>
-    <t>ANTONELLA</t>
-  </si>
-  <si>
     <t>Ayelen Sabrina Romano</t>
   </si>
   <si>
     <t>Maria victoria</t>
   </si>
   <si>
-    <t>Angel Bartolini</t>
-  </si>
-  <si>
-    <t>Caru Villalva</t>
-  </si>
-  <si>
     <t>Carolina Crapanzano</t>
   </si>
   <si>
@@ -664,18 +511,12 @@
     <t>Arevalo Cesar</t>
   </si>
   <si>
-    <t>CESAR A</t>
-  </si>
-  <si>
     <t>Luciano Chiaramonte de Clermont</t>
   </si>
   <si>
     <t>Claudio Fabian Arancibia</t>
   </si>
   <si>
-    <t>Adriana Rueda</t>
-  </si>
-  <si>
     <t>Cristian Emanuel Lopez</t>
   </si>
   <si>
@@ -694,219 +535,177 @@
     <t>Elias</t>
   </si>
   <si>
+    <t>Emanuel Ferrari</t>
+  </si>
+  <si>
+    <t>MATÍAS EZEQUIEL</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Florencia Alejandra</t>
+  </si>
+  <si>
+    <t>Franco Franco</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>Enrique Enrique Enrique</t>
+  </si>
+  <si>
+    <t>Gabriela Acchura Llanos</t>
+  </si>
+  <si>
+    <t>Georgina</t>
+  </si>
+  <si>
+    <t>giuliana antonella</t>
+  </si>
+  <si>
+    <t>Susana Susana</t>
+  </si>
+  <si>
+    <t>Veronica Veronica</t>
+  </si>
+  <si>
+    <t>Ian</t>
+  </si>
+  <si>
+    <t>Carolina Mercedes</t>
+  </si>
+  <si>
+    <t>Laura Esposto</t>
+  </si>
+  <si>
+    <t>Carina leiva</t>
+  </si>
+  <si>
+    <t>Luu Zambrano</t>
+  </si>
+  <si>
+    <t>Marcelo Marcelo</t>
+  </si>
+  <si>
+    <t>Marcela Alejandra Tejerina</t>
+  </si>
+  <si>
+    <t>Maria Laura Carrizo</t>
+  </si>
+  <si>
+    <t>Maria Laura</t>
+  </si>
+  <si>
+    <t>Maricel</t>
+  </si>
+  <si>
+    <t>Guerrero Cabezas Marisel</t>
+  </si>
+  <si>
+    <t>MAURO FEDERICO</t>
+  </si>
+  <si>
+    <t>Anto</t>
+  </si>
+  <si>
+    <t>nolasco meliza</t>
+  </si>
+  <si>
+    <t>Micaela Lotufo Haddad</t>
+  </si>
+  <si>
+    <t>Mario Mario Mario</t>
+  </si>
+  <si>
+    <t>Nadia Garcia</t>
+  </si>
+  <si>
+    <t>Natalia Natalia</t>
+  </si>
+  <si>
+    <t>Claudio lucas primero</t>
+  </si>
+  <si>
+    <t>Natalia Erika Schmid</t>
+  </si>
+  <si>
+    <t>Nicolas Nicolas</t>
+  </si>
+  <si>
+    <t>Noali Elisabeth Garcia</t>
+  </si>
+  <si>
+    <t>Noelia Ruiz</t>
+  </si>
+  <si>
+    <t>Fernanda Fernanda</t>
+  </si>
+  <si>
+    <t>Pablo Pablo Ortiz</t>
+  </si>
+  <si>
+    <t>Pao Rey</t>
+  </si>
+  <si>
+    <t>Pamela Vuistaz</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>Daniela Reynaga</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>Rocio Pelaez</t>
+  </si>
+  <si>
+    <t>Alejandro Ra</t>
+  </si>
+  <si>
+    <t>LAURA NATALIA</t>
+  </si>
+  <si>
+    <t>Romi B Banega</t>
+  </si>
+  <si>
+    <t>Rosa del carmen</t>
+  </si>
+  <si>
+    <t>Gabriela Gabriela</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>Tam</t>
+  </si>
+  <si>
+    <t>Tarcicio Barboza</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>Valeria Raquel Pastrana</t>
+  </si>
+  <si>
+    <t>VERONICA</t>
+  </si>
+  <si>
+    <t>Jose Jose Jose</t>
+  </si>
+  <si>
+    <t>Marcela Alejandra</t>
+  </si>
+  <si>
     <t>Valeria</t>
   </si>
   <si>
-    <t>Emanuel Ferrari</t>
-  </si>
-  <si>
-    <t>Emi Lopez</t>
-  </si>
-  <si>
-    <t>MATÍAS EZEQUIEL</t>
-  </si>
-  <si>
-    <t>Francisco</t>
-  </si>
-  <si>
-    <t>Flori</t>
-  </si>
-  <si>
-    <t>Florencia Alejandra</t>
-  </si>
-  <si>
-    <t>Franco Franco</t>
-  </si>
-  <si>
-    <t>Franco</t>
-  </si>
-  <si>
-    <t>Stefano Frova</t>
-  </si>
-  <si>
-    <t>Enrique Enrique Enrique</t>
-  </si>
-  <si>
-    <t>Gabriela Acchura Llanos</t>
-  </si>
-  <si>
-    <t>Georgina</t>
-  </si>
-  <si>
-    <t>giuliana antonella</t>
-  </si>
-  <si>
-    <t>Susana Susana</t>
-  </si>
-  <si>
-    <t>Celeste Rodriguez Simon</t>
-  </si>
-  <si>
-    <t>Mejorge</t>
-  </si>
-  <si>
-    <t>Jorgelina</t>
-  </si>
-  <si>
-    <t>Veronica Veronica</t>
-  </si>
-  <si>
-    <t>Ian</t>
-  </si>
-  <si>
-    <t>Carolina Mercedes</t>
-  </si>
-  <si>
-    <t>Martina Portella</t>
-  </si>
-  <si>
-    <t>Laura Esposto</t>
-  </si>
-  <si>
-    <t>Carina leiva</t>
-  </si>
-  <si>
-    <t>Luu Zambrano</t>
-  </si>
-  <si>
-    <t>Marcelo Marcelo</t>
-  </si>
-  <si>
-    <t>Marcela Alejandra Tejerina</t>
-  </si>
-  <si>
-    <t>Maria Laura Carrizo</t>
-  </si>
-  <si>
-    <t>Maria Laura</t>
-  </si>
-  <si>
-    <t>Maricel</t>
-  </si>
-  <si>
-    <t>Guerrero Cabezas Marisel</t>
-  </si>
-  <si>
-    <t>Mati Orellana</t>
-  </si>
-  <si>
-    <t>MAURO FEDERICO</t>
-  </si>
-  <si>
-    <t>Anto</t>
-  </si>
-  <si>
-    <t>nolasco meliza</t>
-  </si>
-  <si>
-    <t>Micaela Lotufo Haddad</t>
-  </si>
-  <si>
-    <t>Mario Mario Mario</t>
-  </si>
-  <si>
-    <t>Nadia Garcia</t>
-  </si>
-  <si>
-    <t>Natalia Natalia</t>
-  </si>
-  <si>
-    <t>Claudio lucas primero</t>
-  </si>
-  <si>
-    <t>Natalia Erika Schmid</t>
-  </si>
-  <si>
-    <t>Nicolas Nicolas</t>
-  </si>
-  <si>
-    <t>Noali Elisabeth Garcia</t>
-  </si>
-  <si>
-    <t>Noelia Ruiz</t>
-  </si>
-  <si>
-    <t>Pablo</t>
-  </si>
-  <si>
-    <t>Pablo Pablo Ortiz</t>
-  </si>
-  <si>
-    <t>Pao Rey</t>
-  </si>
-  <si>
-    <t>Auchana Pau</t>
-  </si>
-  <si>
-    <t>Macarena Rodriguez</t>
-  </si>
-  <si>
-    <t>Pamela Vuistaz</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>Yamila Retamar</t>
-  </si>
-  <si>
-    <t>Ly</t>
-  </si>
-  <si>
-    <t>Daniela Reynaga</t>
-  </si>
-  <si>
-    <t>Roberto</t>
-  </si>
-  <si>
-    <t>Rocio Pelaez</t>
-  </si>
-  <si>
-    <t>Alejandro Ra</t>
-  </si>
-  <si>
-    <t>LAURA NATALIA</t>
-  </si>
-  <si>
-    <t>Romi B Banega</t>
-  </si>
-  <si>
-    <t>Romina Sanchez</t>
-  </si>
-  <si>
-    <t>Rosa del carmen</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>Sol Valdez</t>
-  </si>
-  <si>
-    <t>Tam</t>
-  </si>
-  <si>
-    <t>Tarcicio Barboza</t>
-  </si>
-  <si>
-    <t>Victoria</t>
-  </si>
-  <si>
-    <t>Valeria Raquel Pastrana</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
-  </si>
-  <si>
-    <t>Jose Jose Jose</t>
-  </si>
-  <si>
-    <t>Marcela Alejandra</t>
-  </si>
-  <si>
-    <t>Ye</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -916,39 +715,39 @@
     <t>18.0</t>
   </si>
   <si>
+    <t>3.0 -&gt; 3.0</t>
+  </si>
+  <si>
+    <t>3.0 -&gt; Desconocido</t>
+  </si>
+  <si>
+    <t>3.0 -&gt; 477.0</t>
+  </si>
+  <si>
+    <t>3.0 -&gt; 18.0</t>
+  </si>
+  <si>
+    <t>37.0 -&gt; 37.0 -&gt; 907.0</t>
+  </si>
+  <si>
+    <t>18.0 -&gt; 18.0 -&gt; 18.0</t>
+  </si>
+  <si>
+    <t>907.0 -&gt; 907.0</t>
+  </si>
+  <si>
+    <t>Desconocido</t>
+  </si>
+  <si>
     <t>3.0</t>
   </si>
   <si>
-    <t>3.0 -&gt; 3.0</t>
-  </si>
-  <si>
-    <t>3.0 -&gt; Desconocido</t>
-  </si>
-  <si>
-    <t>3.0 -&gt; 477.0</t>
-  </si>
-  <si>
-    <t>3.0 -&gt; 18.0</t>
-  </si>
-  <si>
-    <t>37.0 -&gt; 37.0 -&gt; 907.0</t>
-  </si>
-  <si>
-    <t>18.0 -&gt; 18.0 -&gt; 18.0</t>
-  </si>
-  <si>
-    <t>907.0 -&gt; 907.0</t>
-  </si>
-  <si>
-    <t>Desconocido</t>
+    <t>103.0</t>
   </si>
   <si>
     <t>4.0</t>
   </si>
   <si>
-    <t>103.0</t>
-  </si>
-  <si>
     <t>103.0 -&gt; 4.0 -&gt; 503.0</t>
   </si>
   <si>
@@ -971,12 +770,6 @@
   </si>
   <si>
     <t>907.0</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>18.0 -&gt; 4.0</t>
   </si>
   <si>
     <t>18.0 -&gt; 18.0 -&gt; 18.0 -&gt; 18.0 -&gt; 18.0</t>
@@ -1368,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1414,7 +1207,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="C2">
         <v>17940368</v>
@@ -1429,19 +1222,19 @@
         <v>46001</v>
       </c>
       <c r="H2" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I2" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J2" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K2" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L2" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1449,37 +1242,37 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="C3">
-        <v>2120618</v>
+        <v>22946409</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2">
-        <v>46068</v>
+        <v>45659</v>
       </c>
       <c r="F3" s="2">
-        <v>46052</v>
+        <v>46007</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="H3" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I3" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="J3" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K3" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="L3" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1487,37 +1280,37 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="C4">
-        <v>2181822</v>
+        <v>24790890</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2">
-        <v>46071</v>
+        <v>45866</v>
       </c>
       <c r="F4" s="2">
-        <v>46052</v>
+        <v>45961</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H4" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I4" t="s">
-        <v>300</v>
+        <v>234</v>
       </c>
       <c r="J4" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K4" t="s">
-        <v>327</v>
+        <v>240</v>
       </c>
       <c r="L4" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1525,37 +1318,37 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="C5">
-        <v>2242819</v>
+        <v>25009560</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>46079</v>
+        <v>45909</v>
       </c>
       <c r="F5" s="2">
-        <v>46052</v>
+        <v>46001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I5" t="s">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="J5" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K5" t="s">
-        <v>327</v>
+        <v>259</v>
       </c>
       <c r="L5" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1563,37 +1356,37 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="C6">
-        <v>2264822</v>
+        <v>25118778</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2">
-        <v>46080</v>
+        <v>45634</v>
       </c>
       <c r="F6" s="2">
-        <v>46052</v>
+        <v>45989</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="H6" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I6" t="s">
-        <v>300</v>
+        <v>236</v>
       </c>
       <c r="J6" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K6" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L6" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1601,37 +1394,37 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="C7">
-        <v>22946409</v>
+        <v>26057054</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2">
-        <v>45659</v>
+        <v>45656</v>
       </c>
       <c r="F7" s="2">
-        <v>46007</v>
+        <v>46052</v>
       </c>
       <c r="G7">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="H7" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I7" t="s">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="J7" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="K7" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="L7" t="s">
-        <v>327</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1639,37 +1432,37 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C8">
-        <v>24790890</v>
+        <v>26131584</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2">
-        <v>45866</v>
+        <v>45649</v>
       </c>
       <c r="F8" s="2">
-        <v>45961</v>
+        <v>46017</v>
       </c>
       <c r="G8">
-        <v>95</v>
+        <v>368</v>
       </c>
       <c r="H8" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I8" t="s">
-        <v>302</v>
+        <v>238</v>
       </c>
       <c r="J8" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K8" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="L8" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1677,37 +1470,34 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="C9">
-        <v>25009560</v>
+        <v>28566147</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>45909</v>
+        <v>46074</v>
       </c>
       <c r="F9" s="2">
-        <v>46001</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
+        <v>46030</v>
       </c>
       <c r="H9" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I9" t="s">
-        <v>303</v>
+        <v>232</v>
       </c>
       <c r="J9" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K9" t="s">
-        <v>328</v>
+        <v>258</v>
       </c>
       <c r="L9" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1715,37 +1505,37 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="C10">
-        <v>25118778</v>
+        <v>29336116</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>45634</v>
+        <v>46023</v>
       </c>
       <c r="F10" s="2">
-        <v>45989</v>
+        <v>46029</v>
       </c>
       <c r="G10">
-        <v>355</v>
+        <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I10" t="s">
-        <v>304</v>
+        <v>239</v>
       </c>
       <c r="J10" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="K10" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="L10" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1753,37 +1543,34 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="C11">
-        <v>25457311</v>
+        <v>30103833</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="F11" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+        <v>45989</v>
       </c>
       <c r="H11" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I11" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="J11" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K11" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L11" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1791,37 +1578,37 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C12">
-        <v>26057054</v>
+        <v>30766482</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2">
-        <v>45656</v>
+        <v>46023</v>
       </c>
       <c r="F12" s="2">
         <v>46052</v>
       </c>
       <c r="G12">
-        <v>396</v>
+        <v>29</v>
       </c>
       <c r="H12" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I12" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
       <c r="J12" t="s">
-        <v>325</v>
+        <v>241</v>
       </c>
       <c r="K12" t="s">
-        <v>325</v>
+        <v>241</v>
       </c>
       <c r="L12" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1829,37 +1616,37 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="C13">
-        <v>26131584</v>
+        <v>31788443</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2">
-        <v>45649</v>
+        <v>45831</v>
       </c>
       <c r="F13" s="2">
-        <v>46017</v>
+        <v>45991</v>
       </c>
       <c r="G13">
-        <v>368</v>
+        <v>160</v>
       </c>
       <c r="H13" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I13" t="s">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="J13" t="s">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="K13" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="L13" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1867,37 +1654,37 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="C14">
-        <v>26936108</v>
+        <v>31949090</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="2">
-        <v>46080</v>
+        <v>45750</v>
       </c>
       <c r="F14" s="2">
-        <v>46056</v>
+        <v>46044</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="H14" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I14" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="J14" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K14" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L14" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1905,34 +1692,34 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="C15">
-        <v>28566147</v>
+        <v>32534579</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>46074</v>
+        <v>45659</v>
       </c>
       <c r="F15" s="2">
-        <v>46030</v>
+        <v>46013</v>
       </c>
       <c r="H15" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I15" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="J15" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="K15" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L15" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1940,37 +1727,37 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C16">
-        <v>29336116</v>
+        <v>33753144</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>46023</v>
+        <v>45639</v>
       </c>
       <c r="F16" s="2">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>385</v>
       </c>
       <c r="H16" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I16" t="s">
-        <v>307</v>
+        <v>243</v>
       </c>
       <c r="J16" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="K16" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="L16" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1978,34 +1765,37 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="C17">
-        <v>30103833</v>
+        <v>34524241</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2">
-        <v>46078</v>
+        <v>45634</v>
       </c>
       <c r="F17" s="2">
-        <v>45989</v>
+        <v>46058</v>
+      </c>
+      <c r="G17">
+        <v>424</v>
       </c>
       <c r="H17" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I17" t="s">
-        <v>308</v>
+        <v>244</v>
       </c>
       <c r="J17" t="s">
-        <v>308</v>
+        <v>242</v>
       </c>
       <c r="K17" t="s">
-        <v>327</v>
+        <v>243</v>
       </c>
       <c r="L17" t="s">
-        <v>327</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2013,37 +1803,37 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C18">
-        <v>30348383</v>
+        <v>35482130</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2">
-        <v>46074</v>
+        <v>45652</v>
       </c>
       <c r="F18" s="2">
-        <v>46056</v>
+        <v>46059</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="H18" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I18" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="J18" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="K18" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="L18" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2051,37 +1841,37 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C19">
-        <v>30766482</v>
+        <v>36345824</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2">
-        <v>46023</v>
+        <v>45985</v>
       </c>
       <c r="F19" s="2">
-        <v>46052</v>
+        <v>45989</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I19" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="J19" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K19" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="L19" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2089,37 +1879,34 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="C20">
-        <v>30806219</v>
+        <v>36379096</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" s="2">
-        <v>45681</v>
+        <v>45740</v>
       </c>
       <c r="F20" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G20">
-        <v>375</v>
+        <v>46062</v>
       </c>
       <c r="H20" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I20" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="J20" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="K20" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L20" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2127,37 +1914,34 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="C21">
-        <v>31788443</v>
+        <v>37105548</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21" s="2">
-        <v>45831</v>
+        <v>45816</v>
       </c>
       <c r="F21" s="2">
-        <v>45991</v>
-      </c>
-      <c r="G21">
-        <v>160</v>
+        <v>46053</v>
       </c>
       <c r="H21" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I21" t="s">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="J21" t="s">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="K21" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L21" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2165,37 +1949,37 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C22">
-        <v>31949090</v>
+        <v>37729574</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" s="2">
-        <v>45750</v>
+        <v>45995</v>
       </c>
       <c r="F22" s="2">
-        <v>46044</v>
+        <v>46031</v>
       </c>
       <c r="G22">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I22" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="J22" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="K22" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L22" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2203,34 +1987,37 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="C23">
-        <v>32534579</v>
+        <v>38032739</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>45659</v>
+        <v>45688</v>
       </c>
       <c r="F23" s="2">
-        <v>46013</v>
+        <v>46009</v>
+      </c>
+      <c r="G23">
+        <v>321</v>
       </c>
       <c r="H23" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I23" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="J23" t="s">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="K23" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2238,37 +2025,34 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C24">
-        <v>32914047</v>
+        <v>38035015</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>46078</v>
+        <v>45860</v>
       </c>
       <c r="F24" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
+        <v>46031</v>
       </c>
       <c r="H24" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I24" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="J24" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K24" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L24" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2276,37 +2060,37 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="C25">
-        <v>33753144</v>
+        <v>38184239</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25" s="2">
-        <v>45639</v>
+        <v>45993</v>
       </c>
       <c r="F25" s="2">
-        <v>46024</v>
+        <v>46003</v>
       </c>
       <c r="G25">
-        <v>385</v>
+        <v>10</v>
       </c>
       <c r="H25" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I25" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="J25" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="K25" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2314,37 +2098,37 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="C26">
-        <v>34524241</v>
+        <v>38738650</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2">
-        <v>45634</v>
+        <v>45913</v>
       </c>
       <c r="F26" s="2">
-        <v>46058</v>
+        <v>46032</v>
       </c>
       <c r="G26">
-        <v>424</v>
+        <v>119</v>
       </c>
       <c r="H26" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I26" t="s">
-        <v>311</v>
+        <v>233</v>
       </c>
       <c r="J26" t="s">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="K26" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s">
-        <v>330</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2352,37 +2136,37 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="C27">
-        <v>35482130</v>
+        <v>39004179</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" s="2">
-        <v>45652</v>
+        <v>46042</v>
       </c>
       <c r="F27" s="2">
         <v>46059</v>
       </c>
       <c r="G27">
-        <v>407</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I27" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="J27" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="K27" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2390,37 +2174,37 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="C28">
-        <v>35599473</v>
+        <v>39320904</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2">
-        <v>46049</v>
+        <v>45810</v>
       </c>
       <c r="F28" s="2">
-        <v>46056</v>
+        <v>46008</v>
       </c>
       <c r="G28">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="H28" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I28" t="s">
-        <v>308</v>
+        <v>233</v>
       </c>
       <c r="J28" t="s">
-        <v>308</v>
+        <v>241</v>
       </c>
       <c r="K28" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="L28" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2428,37 +2212,37 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="C29">
-        <v>36345824</v>
+        <v>40934003</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" s="2">
-        <v>45985</v>
+        <v>45911</v>
       </c>
       <c r="F29" s="2">
-        <v>45989</v>
+        <v>46066</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="H29" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I29" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="J29" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K29" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L29" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2466,34 +2250,37 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="C30">
-        <v>36379096</v>
+        <v>40934059</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2">
-        <v>45740</v>
+        <v>45987</v>
       </c>
       <c r="F30" s="2">
-        <v>46062</v>
+        <v>46008</v>
+      </c>
+      <c r="G30">
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I30" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="J30" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K30" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2501,34 +2288,37 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="C31">
-        <v>37105548</v>
+        <v>41035709</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" s="2">
-        <v>45816</v>
+        <v>45929</v>
       </c>
       <c r="F31" s="2">
-        <v>46053</v>
+        <v>46021</v>
+      </c>
+      <c r="G31">
+        <v>92</v>
       </c>
       <c r="H31" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I31" t="s">
-        <v>312</v>
+        <v>240</v>
       </c>
       <c r="J31" t="s">
-        <v>312</v>
+        <v>240</v>
       </c>
       <c r="K31" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L31" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2536,37 +2326,37 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32">
+        <v>44327105</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45819</v>
+      </c>
+      <c r="F32" s="2">
+        <v>46006</v>
+      </c>
+      <c r="G32">
         <v>187</v>
       </c>
-      <c r="C32">
-        <v>37729574</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" s="2">
-        <v>45995</v>
-      </c>
-      <c r="F32" s="2">
-        <v>46031</v>
-      </c>
-      <c r="G32">
-        <v>36</v>
-      </c>
       <c r="H32" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I32" t="s">
-        <v>313</v>
+        <v>248</v>
       </c>
       <c r="J32" t="s">
-        <v>313</v>
+        <v>248</v>
       </c>
       <c r="K32" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L32" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2574,37 +2364,34 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="C33">
-        <v>38032739</v>
+        <v>44744527</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="2">
-        <v>45688</v>
+        <v>45629</v>
       </c>
       <c r="F33" s="2">
-        <v>46009</v>
-      </c>
-      <c r="G33">
-        <v>321</v>
+        <v>45992</v>
       </c>
       <c r="H33" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I33" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="J33" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K33" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="L33" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2612,34 +2399,34 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="C34">
-        <v>38035015</v>
+        <v>45771238</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <v>45860</v>
+        <v>45638</v>
       </c>
       <c r="F34" s="2">
-        <v>46031</v>
+        <v>46056</v>
       </c>
       <c r="H34" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I34" t="s">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="J34" t="s">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="K34" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2647,37 +2434,34 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="C35">
-        <v>38184239</v>
+        <v>45849671</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" s="2">
-        <v>45993</v>
+        <v>45870</v>
       </c>
       <c r="F35" s="2">
-        <v>46003</v>
-      </c>
-      <c r="G35">
-        <v>10</v>
+        <v>46027</v>
       </c>
       <c r="H35" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I35" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="J35" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="K35" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L35" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2685,37 +2469,31 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
-      </c>
-      <c r="C36">
-        <v>38738650</v>
+        <v>156</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2">
-        <v>45913</v>
+        <v>46043</v>
       </c>
       <c r="F36" s="2">
-        <v>46032</v>
-      </c>
-      <c r="G36">
-        <v>119</v>
+        <v>46037</v>
       </c>
       <c r="H36" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I36" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="J36" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K36" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="L36" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2723,37 +2501,31 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>192</v>
-      </c>
-      <c r="C37">
-        <v>39004179</v>
+        <v>157</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" s="2">
-        <v>46042</v>
+        <v>45856</v>
       </c>
       <c r="F37" s="2">
-        <v>46059</v>
-      </c>
-      <c r="G37">
-        <v>17</v>
+        <v>46007</v>
       </c>
       <c r="H37" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I37" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="J37" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K37" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L37" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2761,37 +2533,31 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
-      </c>
-      <c r="C38">
-        <v>39320904</v>
+        <v>158</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2">
-        <v>45810</v>
+        <v>45674</v>
       </c>
       <c r="F38" s="2">
-        <v>46008</v>
-      </c>
-      <c r="G38">
-        <v>198</v>
+        <v>45996</v>
       </c>
       <c r="H38" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I38" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="J38" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K38" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2799,37 +2565,31 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
-      </c>
-      <c r="C39">
-        <v>40934003</v>
+        <v>159</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" s="2">
-        <v>45911</v>
+        <v>46024</v>
       </c>
       <c r="F39" s="2">
-        <v>46066</v>
-      </c>
-      <c r="G39">
-        <v>155</v>
+        <v>45988</v>
       </c>
       <c r="H39" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I39" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="J39" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="K39" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2837,37 +2597,34 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
-      </c>
-      <c r="C40">
-        <v>40934059</v>
+        <v>160</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2">
-        <v>45987</v>
+        <v>46006</v>
       </c>
       <c r="F40" s="2">
         <v>46008</v>
       </c>
       <c r="G40">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I40" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="J40" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K40" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="L40" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2875,37 +2632,31 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
-      </c>
-      <c r="C41">
-        <v>41035709</v>
+        <v>161</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41" s="2">
-        <v>45929</v>
+        <v>46078</v>
       </c>
       <c r="F41" s="2">
-        <v>46021</v>
-      </c>
-      <c r="G41">
-        <v>92</v>
+        <v>46010</v>
       </c>
       <c r="H41" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I41" t="s">
-        <v>308</v>
+        <v>241</v>
       </c>
       <c r="J41" t="s">
-        <v>308</v>
+        <v>241</v>
       </c>
       <c r="K41" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L41" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2913,37 +2664,31 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
-      </c>
-      <c r="C42">
-        <v>44327105</v>
+        <v>162</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" s="2">
-        <v>45819</v>
+        <v>46001</v>
       </c>
       <c r="F42" s="2">
-        <v>46006</v>
-      </c>
-      <c r="G42">
-        <v>187</v>
+        <v>45995</v>
       </c>
       <c r="H42" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I42" t="s">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="J42" t="s">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="K42" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L42" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2951,34 +2696,31 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>198</v>
-      </c>
-      <c r="C43">
-        <v>44744527</v>
+        <v>163</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" s="2">
-        <v>45629</v>
+        <v>45637</v>
       </c>
       <c r="F43" s="2">
-        <v>45992</v>
+        <v>46012</v>
       </c>
       <c r="H43" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I43" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J43" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K43" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L43" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2986,37 +2728,34 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
-      </c>
-      <c r="C44">
-        <v>4518359</v>
+        <v>164</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2">
-        <v>46080</v>
+        <v>45633</v>
       </c>
       <c r="F44" s="2">
-        <v>46052</v>
+        <v>46009</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="H44" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I44" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="J44" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K44" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L44" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -3024,34 +2763,34 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
-      </c>
-      <c r="C45">
-        <v>45849671</v>
+        <v>165</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" s="2">
-        <v>45870</v>
+        <v>45831</v>
       </c>
       <c r="F45" s="2">
-        <v>46027</v>
+        <v>46052</v>
+      </c>
+      <c r="G45">
+        <v>221</v>
       </c>
       <c r="H45" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I45" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="J45" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K45" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L45" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -3059,37 +2798,31 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>200</v>
-      </c>
-      <c r="C46">
-        <v>4658448</v>
+        <v>166</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46" s="2">
-        <v>46074</v>
+        <v>45913</v>
       </c>
       <c r="F46" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
+        <v>46058</v>
       </c>
       <c r="H46" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I46" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="J46" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K46" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L46" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -3097,37 +2830,34 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C47">
-        <v>4869437</v>
+        <v>167</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47" s="2">
-        <v>46081</v>
+        <v>45634</v>
       </c>
       <c r="F47" s="2">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="H47" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I47" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="J47" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K47" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L47" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -3135,37 +2865,34 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>202</v>
-      </c>
-      <c r="C48">
-        <v>5679726</v>
+        <v>168</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2">
-        <v>46073</v>
+        <v>45911</v>
       </c>
       <c r="F48" s="2">
-        <v>46052</v>
+        <v>46009</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H48" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I48" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="J48" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K48" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -3173,31 +2900,31 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
       <c r="E49" s="2">
-        <v>46043</v>
+        <v>45849</v>
       </c>
       <c r="F49" s="2">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="H49" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I49" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J49" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K49" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L49" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -3205,34 +2932,34 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50" s="2">
-        <v>45913</v>
+        <v>45925</v>
       </c>
       <c r="F50" s="2">
-        <v>46052</v>
+        <v>46031</v>
       </c>
       <c r="G50">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="H50" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I50" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J50" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K50" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L50" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3240,31 +2967,34 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="2">
-        <v>45856</v>
+        <v>45849</v>
       </c>
       <c r="F51" s="2">
-        <v>46007</v>
+        <v>46009</v>
+      </c>
+      <c r="G51">
+        <v>160</v>
       </c>
       <c r="H51" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I51" t="s">
-        <v>299</v>
+        <v>233</v>
       </c>
       <c r="J51" t="s">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="K51" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="L51" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3272,31 +3002,34 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
       <c r="E52" s="2">
-        <v>45674</v>
+        <v>45927</v>
       </c>
       <c r="F52" s="2">
-        <v>45996</v>
+        <v>46049</v>
+      </c>
+      <c r="G52">
+        <v>122</v>
       </c>
       <c r="H52" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I52" t="s">
-        <v>299</v>
+        <v>249</v>
       </c>
       <c r="J52" t="s">
-        <v>299</v>
+        <v>249</v>
       </c>
       <c r="K52" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L52" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3304,31 +3037,34 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="E53" s="2">
-        <v>46024</v>
+        <v>46002</v>
       </c>
       <c r="F53" s="2">
-        <v>45988</v>
+        <v>46044</v>
+      </c>
+      <c r="G53">
+        <v>42</v>
       </c>
       <c r="H53" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I53" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J53" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K53" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L53" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3336,34 +3072,31 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54" s="2">
-        <v>45867</v>
+        <v>46033</v>
       </c>
       <c r="F54" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G54">
-        <v>189</v>
+        <v>45991</v>
       </c>
       <c r="H54" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I54" t="s">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="J54" t="s">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="K54" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L54" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3371,34 +3104,34 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="2">
-        <v>46006</v>
+        <v>46021</v>
       </c>
       <c r="F55" s="2">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I55" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="J55" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="K55" t="s">
-        <v>327</v>
+        <v>260</v>
       </c>
       <c r="L55" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3406,31 +3139,31 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56" s="2">
-        <v>46078</v>
+        <v>46056</v>
       </c>
       <c r="F56" s="2">
-        <v>46010</v>
+        <v>46023</v>
       </c>
       <c r="H56" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I56" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="J56" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="K56" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L56" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3438,34 +3171,31 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57" s="2">
-        <v>46073</v>
+        <v>45731</v>
       </c>
       <c r="F57" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
+        <v>45994</v>
       </c>
       <c r="H57" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I57" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J57" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K57" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L57" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3473,34 +3203,31 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" s="2">
-        <v>45652</v>
+        <v>46037</v>
       </c>
       <c r="F58" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G58">
-        <v>404</v>
+        <v>46029</v>
       </c>
       <c r="H58" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I58" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="J58" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="K58" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L58" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3508,31 +3235,31 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59" s="2">
-        <v>46001</v>
+        <v>45831</v>
       </c>
       <c r="F59" s="2">
-        <v>45995</v>
+        <v>46013</v>
       </c>
       <c r="H59" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I59" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J59" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K59" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L59" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3540,31 +3267,34 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="E60" s="2">
-        <v>45637</v>
+        <v>45942</v>
       </c>
       <c r="F60" s="2">
-        <v>46012</v>
+        <v>46010</v>
+      </c>
+      <c r="G60">
+        <v>68</v>
       </c>
       <c r="H60" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I60" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J60" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K60" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L60" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3572,34 +3302,31 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="2">
-        <v>45633</v>
+        <v>46029</v>
       </c>
       <c r="F61" s="2">
-        <v>46009</v>
-      </c>
-      <c r="G61">
-        <v>376</v>
+        <v>46008</v>
       </c>
       <c r="H61" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I61" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="J61" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K61" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="L61" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3607,34 +3334,31 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
       <c r="E62" s="2">
-        <v>46074</v>
+        <v>46052</v>
       </c>
       <c r="F62" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
+        <v>46010</v>
       </c>
       <c r="H62" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I62" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="J62" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="K62" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L62" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3642,34 +3366,31 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" s="2">
-        <v>45831</v>
+        <v>46023</v>
       </c>
       <c r="F63" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G63">
-        <v>221</v>
+        <v>46064</v>
       </c>
       <c r="H63" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I63" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J63" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K63" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L63" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3677,31 +3398,31 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
       <c r="E64" s="2">
-        <v>45913</v>
+        <v>46039</v>
       </c>
       <c r="F64" s="2">
-        <v>46058</v>
+        <v>45993</v>
       </c>
       <c r="H64" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I64" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J64" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K64" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L64" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3709,34 +3430,34 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65" s="2">
-        <v>45904</v>
+        <v>45660</v>
       </c>
       <c r="F65" s="2">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="G65">
-        <v>152</v>
+        <v>392</v>
       </c>
       <c r="H65" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I65" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J65" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K65" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L65" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3744,34 +3465,31 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" s="2">
-        <v>45634</v>
+        <v>45734</v>
       </c>
       <c r="F66" s="2">
-        <v>46064</v>
-      </c>
-      <c r="G66">
-        <v>430</v>
+        <v>45986</v>
       </c>
       <c r="H66" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I66" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J66" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K66" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L66" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3779,34 +3497,31 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="2">
-        <v>45911</v>
+        <v>46017</v>
       </c>
       <c r="F67" s="2">
-        <v>46009</v>
-      </c>
-      <c r="G67">
-        <v>98</v>
+        <v>46011</v>
       </c>
       <c r="H67" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I67" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="J67" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K67" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="L67" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3814,66 +3529,66 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68" s="2">
-        <v>45849</v>
+        <v>45930</v>
       </c>
       <c r="F68" s="2">
-        <v>46031</v>
+        <v>46052</v>
+      </c>
+      <c r="G68">
+        <v>122</v>
       </c>
       <c r="H68" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I68" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J68" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K68" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L68" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
         <v>79</v>
       </c>
-      <c r="B69" t="s">
-        <v>223</v>
-      </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69" s="2">
-        <v>45925</v>
+        <v>46069</v>
       </c>
       <c r="F69" s="2">
         <v>46031</v>
       </c>
       <c r="G69">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I69" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="J69" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="K69" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L69" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3881,34 +3596,34 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="2">
-        <v>45849</v>
+        <v>45912</v>
       </c>
       <c r="F70" s="2">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="G70">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="H70" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I70" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="J70" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="K70" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="L70" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3916,34 +3631,31 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71" s="2">
-        <v>45927</v>
+        <v>45973</v>
       </c>
       <c r="F71" s="2">
-        <v>46049</v>
-      </c>
-      <c r="G71">
-        <v>122</v>
+        <v>45986</v>
       </c>
       <c r="H71" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I71" t="s">
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="J71" t="s">
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="K71" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L71" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3951,34 +3663,34 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="2">
-        <v>45978</v>
+        <v>45639</v>
       </c>
       <c r="F72" s="2">
-        <v>46052</v>
+        <v>45992</v>
       </c>
       <c r="G72">
-        <v>74</v>
+        <v>353</v>
       </c>
       <c r="H72" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I72" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="J72" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K72" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="L72" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3986,34 +3698,31 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
       <c r="E73" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="F73" s="2">
-        <v>46044</v>
-      </c>
-      <c r="G73">
-        <v>42</v>
+        <v>46007</v>
       </c>
       <c r="H73" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I73" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J73" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K73" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L73" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4021,34 +3730,34 @@
         <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74" s="2">
-        <v>46076</v>
+        <v>45840</v>
       </c>
       <c r="F74" s="2">
-        <v>46056</v>
+        <v>46001</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="H74" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I74" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J74" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K74" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L74" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -4056,66 +3765,66 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75" s="2">
-        <v>46033</v>
+        <v>45864</v>
       </c>
       <c r="F75" s="2">
-        <v>45991</v>
+        <v>46056</v>
+      </c>
+      <c r="G75">
+        <v>192</v>
       </c>
       <c r="H75" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I75" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="J75" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="K75" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L75" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
         <v>86</v>
       </c>
-      <c r="B76" t="s">
-        <v>230</v>
-      </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="2">
-        <v>46021</v>
+        <v>46001</v>
       </c>
       <c r="F76" s="2">
-        <v>46024</v>
+        <v>46065</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="H76" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I76" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="J76" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="K76" t="s">
-        <v>329</v>
+        <v>258</v>
       </c>
       <c r="L76" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4123,34 +3832,34 @@
         <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="2">
-        <v>45784</v>
+        <v>45908</v>
       </c>
       <c r="F77" s="2">
-        <v>46056</v>
+        <v>46001</v>
       </c>
       <c r="G77">
-        <v>272</v>
+        <v>93</v>
       </c>
       <c r="H77" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I77" t="s">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="J77" t="s">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="K77" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L77" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4158,31 +3867,31 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78" s="2">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="F78" s="2">
-        <v>46023</v>
+        <v>46009</v>
       </c>
       <c r="H78" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I78" t="s">
-        <v>309</v>
+        <v>243</v>
       </c>
       <c r="J78" t="s">
-        <v>309</v>
+        <v>243</v>
       </c>
       <c r="K78" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L78" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4190,31 +3899,31 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" s="2">
-        <v>45731</v>
+        <v>46071</v>
       </c>
       <c r="F79" s="2">
-        <v>45994</v>
+        <v>45986</v>
       </c>
       <c r="H79" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I79" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J79" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K79" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L79" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4222,31 +3931,34 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" s="2">
-        <v>46037</v>
+        <v>45984</v>
       </c>
       <c r="F80" s="2">
-        <v>46029</v>
+        <v>46008</v>
+      </c>
+      <c r="G80">
+        <v>24</v>
       </c>
       <c r="H80" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I80" t="s">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="J80" t="s">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="K80" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L80" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -4254,34 +3966,34 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="2">
-        <v>45872</v>
+        <v>45902</v>
       </c>
       <c r="F81" s="2">
-        <v>46056</v>
+        <v>46044</v>
       </c>
       <c r="G81">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="H81" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I81" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="J81" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K81" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="L81" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4289,31 +4001,31 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82" s="2">
-        <v>45831</v>
+        <v>45931</v>
       </c>
       <c r="F82" s="2">
-        <v>46013</v>
+        <v>45989</v>
       </c>
       <c r="H82" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I82" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="J82" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="K82" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L82" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4321,34 +4033,31 @@
         <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83" s="2">
-        <v>45942</v>
+        <v>45872</v>
       </c>
       <c r="F83" s="2">
-        <v>46010</v>
-      </c>
-      <c r="G83">
-        <v>68</v>
+        <v>46050</v>
       </c>
       <c r="H83" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I83" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J83" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K83" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L83" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4356,31 +4065,31 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84" s="2">
-        <v>46029</v>
+        <v>46040</v>
       </c>
       <c r="F84" s="2">
-        <v>46008</v>
+        <v>45995</v>
       </c>
       <c r="H84" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I84" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J84" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K84" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L84" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4388,31 +4097,31 @@
         <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85" s="2">
-        <v>46052</v>
+        <v>46042</v>
       </c>
       <c r="F85" s="2">
-        <v>46010</v>
+        <v>45987</v>
       </c>
       <c r="H85" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I85" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="J85" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="K85" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L85" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4420,66 +4129,63 @@
         <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86" s="2">
-        <v>46023</v>
+        <v>46058</v>
       </c>
       <c r="F86" s="2">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="H86" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I86" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J86" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K86" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L86" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
         <v>97</v>
       </c>
-      <c r="B87" t="s">
-        <v>241</v>
-      </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" s="2">
-        <v>45973</v>
+        <v>46063</v>
       </c>
       <c r="F87" s="2">
-        <v>46056</v>
+        <v>45989</v>
       </c>
       <c r="G87">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I87" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="J87" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="K87" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L87" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4487,34 +4193,31 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="D88">
         <v>1</v>
       </c>
       <c r="E88" s="2">
-        <v>46064</v>
+        <v>46050</v>
       </c>
       <c r="F88" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G88">
-        <v>0</v>
+        <v>46044</v>
       </c>
       <c r="H88" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I88" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J88" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K88" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L88" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4522,34 +4225,34 @@
         <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89" s="2">
-        <v>46039</v>
+        <v>45942</v>
       </c>
       <c r="F89" s="2">
-        <v>46056</v>
+        <v>46000</v>
       </c>
       <c r="G89">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H89" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I89" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J89" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K89" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L89" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4557,31 +4260,34 @@
         <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="2">
-        <v>46039</v>
+        <v>45945</v>
       </c>
       <c r="F90" s="2">
-        <v>45993</v>
+        <v>46062</v>
+      </c>
+      <c r="G90">
+        <v>117</v>
       </c>
       <c r="H90" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I90" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="J90" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K90" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L90" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4589,34 +4295,31 @@
         <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91" s="2">
-        <v>45660</v>
+        <v>45647</v>
       </c>
       <c r="F91" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G91">
-        <v>392</v>
+        <v>46007</v>
       </c>
       <c r="H91" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I91" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J91" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K91" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L91" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4624,31 +4327,34 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" s="2">
-        <v>45734</v>
+        <v>45676</v>
       </c>
       <c r="F92" s="2">
-        <v>45986</v>
+        <v>46052</v>
+      </c>
+      <c r="G92">
+        <v>376</v>
       </c>
       <c r="H92" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I92" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J92" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K92" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L92" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4656,34 +4362,34 @@
         <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93" s="2">
-        <v>45998</v>
+        <v>45960</v>
       </c>
       <c r="F93" s="2">
-        <v>46052</v>
+        <v>45996</v>
       </c>
       <c r="G93">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H93" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I93" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J93" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K93" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L93" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4691,31 +4397,34 @@
         <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94" s="2">
-        <v>46017</v>
+        <v>45913</v>
       </c>
       <c r="F94" s="2">
-        <v>46011</v>
+        <v>46010</v>
+      </c>
+      <c r="G94">
+        <v>97</v>
       </c>
       <c r="H94" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I94" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J94" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K94" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L94" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4723,66 +4432,69 @@
         <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95" s="2">
-        <v>45930</v>
+        <v>45821</v>
       </c>
       <c r="F95" s="2">
         <v>46052</v>
       </c>
       <c r="G95">
-        <v>122</v>
+        <v>231</v>
       </c>
       <c r="H95" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I95" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="J95" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="K95" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L95" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
         <v>106</v>
       </c>
+      <c r="B96" t="s">
+        <v>213</v>
+      </c>
       <c r="D96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E96" s="2">
-        <v>46069</v>
+        <v>45674</v>
       </c>
       <c r="F96" s="2">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="H96" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I96" t="s">
-        <v>318</v>
+        <v>252</v>
       </c>
       <c r="J96" t="s">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="K96" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L96" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4790,34 +4502,34 @@
         <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97" s="2">
-        <v>45912</v>
+        <v>45848</v>
       </c>
       <c r="F97" s="2">
-        <v>46010</v>
+        <v>46052</v>
       </c>
       <c r="G97">
-        <v>98</v>
+        <v>204</v>
       </c>
       <c r="H97" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I97" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="J97" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="K97" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L97" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4825,31 +4537,31 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98" s="2">
-        <v>45973</v>
+        <v>45683</v>
       </c>
       <c r="F98" s="2">
-        <v>45986</v>
+        <v>46003</v>
       </c>
       <c r="H98" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I98" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J98" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K98" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L98" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4857,34 +4569,34 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="2">
-        <v>45639</v>
+        <v>45670</v>
       </c>
       <c r="F99" s="2">
-        <v>45992</v>
+        <v>46009</v>
       </c>
       <c r="G99">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="H99" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I99" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="J99" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K99" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="L99" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4892,31 +4604,31 @@
         <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" s="2">
-        <v>45996</v>
+        <v>46041</v>
       </c>
       <c r="F100" s="2">
-        <v>46007</v>
+        <v>46022</v>
       </c>
       <c r="H100" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I100" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="J100" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="K100" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L100" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4924,34 +4636,34 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101" s="2">
-        <v>45840</v>
+        <v>45826</v>
       </c>
       <c r="F101" s="2">
-        <v>46001</v>
+        <v>46042</v>
       </c>
       <c r="G101">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="H101" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I101" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J101" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K101" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L101" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4959,66 +4671,63 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102" s="2">
-        <v>45864</v>
+        <v>46036</v>
       </c>
       <c r="F102" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G102">
-        <v>192</v>
+        <v>46043</v>
       </c>
       <c r="H102" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I102" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="J102" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="K102" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L102" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
         <v>113</v>
       </c>
+      <c r="B103" t="s">
+        <v>220</v>
+      </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103" s="2">
-        <v>46001</v>
+        <v>45995</v>
       </c>
       <c r="F103" s="2">
-        <v>46065</v>
-      </c>
-      <c r="G103">
-        <v>64</v>
+        <v>46003</v>
       </c>
       <c r="H103" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I103" t="s">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="J103" t="s">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="K103" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L103" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -5026,34 +4735,34 @@
         <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="2">
-        <v>45908</v>
+        <v>46058</v>
       </c>
       <c r="F104" s="2">
-        <v>46001</v>
+        <v>45978</v>
       </c>
       <c r="G104">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H104" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I104" t="s">
-        <v>304</v>
+        <v>254</v>
       </c>
       <c r="J104" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="K104" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="L104" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -5061,34 +4770,34 @@
         <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105" s="2">
-        <v>45659</v>
+        <v>46037</v>
       </c>
       <c r="F105" s="2">
-        <v>46056</v>
+        <v>46059</v>
       </c>
       <c r="G105">
-        <v>397</v>
+        <v>22</v>
       </c>
       <c r="H105" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I105" t="s">
-        <v>319</v>
+        <v>241</v>
       </c>
       <c r="J105" t="s">
-        <v>319</v>
+        <v>241</v>
       </c>
       <c r="K105" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L105" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -5096,31 +4805,34 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106" s="2">
-        <v>46057</v>
+        <v>45830</v>
       </c>
       <c r="F106" s="2">
-        <v>46009</v>
+        <v>46052</v>
+      </c>
+      <c r="G106">
+        <v>222</v>
       </c>
       <c r="H106" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I106" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="J106" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="K106" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L106" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -5128,31 +4840,34 @@
         <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="2">
-        <v>46071</v>
+        <v>45980</v>
       </c>
       <c r="F107" s="2">
-        <v>45986</v>
+        <v>45989</v>
+      </c>
+      <c r="G107">
+        <v>9</v>
       </c>
       <c r="H107" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I107" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="J107" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="K107" t="s">
-        <v>327</v>
+        <v>243</v>
       </c>
       <c r="L107" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -5160,34 +4875,34 @@
         <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" s="2">
-        <v>45984</v>
+        <v>45922</v>
       </c>
       <c r="F108" s="2">
-        <v>46008</v>
+        <v>46041</v>
       </c>
       <c r="G108">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="H108" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I108" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J108" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K108" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L108" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -5195,34 +4910,31 @@
         <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109" s="2">
-        <v>45902</v>
+        <v>45973</v>
       </c>
       <c r="F109" s="2">
-        <v>46044</v>
-      </c>
-      <c r="G109">
-        <v>142</v>
+        <v>46006</v>
       </c>
       <c r="H109" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="I109" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J109" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K109" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L109" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -5230,31 +4942,31 @@
         <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110" s="2">
-        <v>45931</v>
+        <v>45671</v>
       </c>
       <c r="F110" s="2">
-        <v>45989</v>
+        <v>46008</v>
       </c>
       <c r="H110" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I110" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="J110" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="K110" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L110" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -5262,31 +4974,31 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111" s="2">
-        <v>45872</v>
+        <v>46072</v>
       </c>
       <c r="F111" s="2">
-        <v>46050</v>
+        <v>46038</v>
       </c>
       <c r="H111" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="I111" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="J111" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="K111" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L111" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -5294,1191 +5006,34 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112" s="2">
-        <v>46040</v>
+        <v>45999</v>
       </c>
       <c r="F112" s="2">
-        <v>45995</v>
+        <v>46002</v>
+      </c>
+      <c r="G112">
+        <v>3</v>
       </c>
       <c r="H112" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="I112" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="J112" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="K112" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="L112" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12">
-      <c r="A113" t="s">
-        <v>123</v>
-      </c>
-      <c r="B113" t="s">
-        <v>265</v>
-      </c>
-      <c r="D113">
-        <v>1</v>
-      </c>
-      <c r="E113" s="2">
-        <v>46042</v>
-      </c>
-      <c r="F113" s="2">
-        <v>45987</v>
-      </c>
-      <c r="H113" t="s">
-        <v>297</v>
-      </c>
-      <c r="I113" t="s">
-        <v>299</v>
-      </c>
-      <c r="J113" t="s">
-        <v>299</v>
-      </c>
-      <c r="K113" t="s">
-        <v>327</v>
-      </c>
-      <c r="L113" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12">
-      <c r="A114" t="s">
-        <v>124</v>
-      </c>
-      <c r="B114" t="s">
-        <v>266</v>
-      </c>
-      <c r="D114">
-        <v>1</v>
-      </c>
-      <c r="E114" s="2">
-        <v>46058</v>
-      </c>
-      <c r="F114" s="2">
-        <v>46065</v>
-      </c>
-      <c r="H114" t="s">
-        <v>297</v>
-      </c>
-      <c r="I114" t="s">
-        <v>299</v>
-      </c>
-      <c r="J114" t="s">
-        <v>299</v>
-      </c>
-      <c r="K114" t="s">
-        <v>327</v>
-      </c>
-      <c r="L114" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12">
-      <c r="A115" t="s">
-        <v>125</v>
-      </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115" s="2">
-        <v>46063</v>
-      </c>
-      <c r="F115" s="2">
-        <v>45989</v>
-      </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115" t="s">
-        <v>298</v>
-      </c>
-      <c r="I115" t="s">
-        <v>318</v>
-      </c>
-      <c r="J115" t="s">
-        <v>318</v>
-      </c>
-      <c r="K115" t="s">
-        <v>327</v>
-      </c>
-      <c r="L115" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12">
-      <c r="A116" t="s">
-        <v>126</v>
-      </c>
-      <c r="B116" t="s">
-        <v>267</v>
-      </c>
-      <c r="D116">
-        <v>1</v>
-      </c>
-      <c r="E116" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F116" s="2">
-        <v>46044</v>
-      </c>
-      <c r="H116" t="s">
-        <v>297</v>
-      </c>
-      <c r="I116" t="s">
-        <v>299</v>
-      </c>
-      <c r="J116" t="s">
-        <v>299</v>
-      </c>
-      <c r="K116" t="s">
-        <v>327</v>
-      </c>
-      <c r="L116" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12">
-      <c r="A117" t="s">
-        <v>127</v>
-      </c>
-      <c r="B117" t="s">
-        <v>268</v>
-      </c>
-      <c r="D117">
-        <v>1</v>
-      </c>
-      <c r="E117" s="2">
-        <v>45942</v>
-      </c>
-      <c r="F117" s="2">
-        <v>46000</v>
-      </c>
-      <c r="G117">
-        <v>58</v>
-      </c>
-      <c r="H117" t="s">
-        <v>298</v>
-      </c>
-      <c r="I117" t="s">
-        <v>299</v>
-      </c>
-      <c r="J117" t="s">
-        <v>299</v>
-      </c>
-      <c r="K117" t="s">
-        <v>327</v>
-      </c>
-      <c r="L117" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12">
-      <c r="A118" t="s">
-        <v>128</v>
-      </c>
-      <c r="B118" t="s">
-        <v>269</v>
-      </c>
-      <c r="D118">
-        <v>2</v>
-      </c>
-      <c r="E118" s="2">
-        <v>45945</v>
-      </c>
-      <c r="F118" s="2">
-        <v>46062</v>
-      </c>
-      <c r="G118">
-        <v>117</v>
-      </c>
-      <c r="H118" t="s">
-        <v>298</v>
-      </c>
-      <c r="I118" t="s">
-        <v>314</v>
-      </c>
-      <c r="J118" t="s">
-        <v>299</v>
-      </c>
-      <c r="K118" t="s">
-        <v>299</v>
-      </c>
-      <c r="L118" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12">
-      <c r="A119" t="s">
-        <v>129</v>
-      </c>
-      <c r="B119" t="s">
-        <v>270</v>
-      </c>
-      <c r="D119">
-        <v>1</v>
-      </c>
-      <c r="E119" s="2">
-        <v>45935</v>
-      </c>
-      <c r="F119" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G119">
-        <v>121</v>
-      </c>
-      <c r="H119" t="s">
-        <v>298</v>
-      </c>
-      <c r="I119" t="s">
-        <v>299</v>
-      </c>
-      <c r="J119" t="s">
-        <v>299</v>
-      </c>
-      <c r="K119" t="s">
-        <v>327</v>
-      </c>
-      <c r="L119" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12">
-      <c r="A120" t="s">
-        <v>130</v>
-      </c>
-      <c r="B120" t="s">
-        <v>271</v>
-      </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="E120" s="2">
-        <v>45676</v>
-      </c>
-      <c r="F120" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G120">
-        <v>376</v>
-      </c>
-      <c r="H120" t="s">
-        <v>298</v>
-      </c>
-      <c r="I120" t="s">
-        <v>299</v>
-      </c>
-      <c r="J120" t="s">
-        <v>299</v>
-      </c>
-      <c r="K120" t="s">
-        <v>327</v>
-      </c>
-      <c r="L120" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12">
-      <c r="A121" t="s">
-        <v>131</v>
-      </c>
-      <c r="B121" t="s">
-        <v>272</v>
-      </c>
-      <c r="D121">
-        <v>1</v>
-      </c>
-      <c r="E121" s="2">
-        <v>45960</v>
-      </c>
-      <c r="F121" s="2">
-        <v>45996</v>
-      </c>
-      <c r="G121">
-        <v>36</v>
-      </c>
-      <c r="H121" t="s">
-        <v>298</v>
-      </c>
-      <c r="I121" t="s">
-        <v>299</v>
-      </c>
-      <c r="J121" t="s">
-        <v>299</v>
-      </c>
-      <c r="K121" t="s">
-        <v>327</v>
-      </c>
-      <c r="L121" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12">
-      <c r="A122" t="s">
-        <v>132</v>
-      </c>
-      <c r="B122" t="s">
-        <v>273</v>
-      </c>
-      <c r="D122">
-        <v>2</v>
-      </c>
-      <c r="E122" s="2">
-        <v>46026</v>
-      </c>
-      <c r="F122" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G122">
-        <v>26</v>
-      </c>
-      <c r="H122" t="s">
-        <v>298</v>
-      </c>
-      <c r="I122" t="s">
-        <v>320</v>
-      </c>
-      <c r="J122" t="s">
-        <v>299</v>
-      </c>
-      <c r="K122" t="s">
-        <v>309</v>
-      </c>
-      <c r="L122" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12">
-      <c r="A123" t="s">
-        <v>133</v>
-      </c>
-      <c r="B123" t="s">
-        <v>274</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123" s="2">
-        <v>45980</v>
-      </c>
-      <c r="F123" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G123">
-        <v>72</v>
-      </c>
-      <c r="H123" t="s">
-        <v>298</v>
-      </c>
-      <c r="I123" t="s">
-        <v>299</v>
-      </c>
-      <c r="J123" t="s">
-        <v>299</v>
-      </c>
-      <c r="K123" t="s">
-        <v>327</v>
-      </c>
-      <c r="L123" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12">
-      <c r="A124" t="s">
-        <v>134</v>
-      </c>
-      <c r="B124" t="s">
-        <v>275</v>
-      </c>
-      <c r="D124">
-        <v>1</v>
-      </c>
-      <c r="E124" s="2">
-        <v>45913</v>
-      </c>
-      <c r="F124" s="2">
-        <v>46010</v>
-      </c>
-      <c r="G124">
-        <v>97</v>
-      </c>
-      <c r="H124" t="s">
-        <v>298</v>
-      </c>
-      <c r="I124" t="s">
-        <v>299</v>
-      </c>
-      <c r="J124" t="s">
-        <v>299</v>
-      </c>
-      <c r="K124" t="s">
-        <v>327</v>
-      </c>
-      <c r="L124" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12">
-      <c r="A125" t="s">
-        <v>135</v>
-      </c>
-      <c r="B125" t="s">
-        <v>276</v>
-      </c>
-      <c r="D125">
-        <v>1</v>
-      </c>
-      <c r="E125" s="2">
-        <v>45821</v>
-      </c>
-      <c r="F125" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G125">
-        <v>231</v>
-      </c>
-      <c r="H125" t="s">
-        <v>298</v>
-      </c>
-      <c r="I125" t="s">
-        <v>310</v>
-      </c>
-      <c r="J125" t="s">
-        <v>310</v>
-      </c>
-      <c r="K125" t="s">
-        <v>327</v>
-      </c>
-      <c r="L125" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12">
-      <c r="A126" t="s">
-        <v>136</v>
-      </c>
-      <c r="B126" t="s">
-        <v>277</v>
-      </c>
-      <c r="D126">
-        <v>1</v>
-      </c>
-      <c r="E126" s="2">
-        <v>46039</v>
-      </c>
-      <c r="F126" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G126">
-        <v>17</v>
-      </c>
-      <c r="H126" t="s">
-        <v>298</v>
-      </c>
-      <c r="I126" t="s">
-        <v>299</v>
-      </c>
-      <c r="J126" t="s">
-        <v>299</v>
-      </c>
-      <c r="K126" t="s">
-        <v>327</v>
-      </c>
-      <c r="L126" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12">
-      <c r="A127" t="s">
-        <v>137</v>
-      </c>
-      <c r="B127" t="s">
-        <v>278</v>
-      </c>
-      <c r="D127">
-        <v>2</v>
-      </c>
-      <c r="E127" s="2">
-        <v>45906</v>
-      </c>
-      <c r="F127" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G127">
-        <v>150</v>
-      </c>
-      <c r="H127" t="s">
-        <v>298</v>
-      </c>
-      <c r="I127" t="s">
-        <v>314</v>
-      </c>
-      <c r="J127" t="s">
-        <v>299</v>
-      </c>
-      <c r="K127" t="s">
-        <v>299</v>
-      </c>
-      <c r="L127" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12">
-      <c r="A128" t="s">
-        <v>138</v>
-      </c>
-      <c r="B128" t="s">
-        <v>279</v>
-      </c>
-      <c r="D128">
-        <v>5</v>
-      </c>
-      <c r="E128" s="2">
-        <v>45674</v>
-      </c>
-      <c r="F128" s="2">
-        <v>46029</v>
-      </c>
-      <c r="G128">
-        <v>355</v>
-      </c>
-      <c r="H128" t="s">
-        <v>298</v>
-      </c>
-      <c r="I128" t="s">
-        <v>321</v>
-      </c>
-      <c r="J128" t="s">
-        <v>299</v>
-      </c>
-      <c r="K128" t="s">
-        <v>299</v>
-      </c>
-      <c r="L128" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12">
-      <c r="A129" t="s">
-        <v>139</v>
-      </c>
-      <c r="B129" t="s">
-        <v>280</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
-      </c>
-      <c r="E129" s="2">
-        <v>45848</v>
-      </c>
-      <c r="F129" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G129">
-        <v>204</v>
-      </c>
-      <c r="H129" t="s">
-        <v>298</v>
-      </c>
-      <c r="I129" t="s">
-        <v>310</v>
-      </c>
-      <c r="J129" t="s">
-        <v>310</v>
-      </c>
-      <c r="K129" t="s">
-        <v>327</v>
-      </c>
-      <c r="L129" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12">
-      <c r="A130" t="s">
-        <v>140</v>
-      </c>
-      <c r="B130" t="s">
-        <v>281</v>
-      </c>
-      <c r="D130">
-        <v>1</v>
-      </c>
-      <c r="E130" s="2">
-        <v>45683</v>
-      </c>
-      <c r="F130" s="2">
-        <v>46003</v>
-      </c>
-      <c r="H130" t="s">
-        <v>297</v>
-      </c>
-      <c r="I130" t="s">
-        <v>299</v>
-      </c>
-      <c r="J130" t="s">
-        <v>299</v>
-      </c>
-      <c r="K130" t="s">
-        <v>327</v>
-      </c>
-      <c r="L130" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12">
-      <c r="A131" t="s">
-        <v>141</v>
-      </c>
-      <c r="B131" t="s">
-        <v>282</v>
-      </c>
-      <c r="D131">
-        <v>2</v>
-      </c>
-      <c r="E131" s="2">
-        <v>45670</v>
-      </c>
-      <c r="F131" s="2">
-        <v>46009</v>
-      </c>
-      <c r="G131">
-        <v>339</v>
-      </c>
-      <c r="H131" t="s">
-        <v>298</v>
-      </c>
-      <c r="I131" t="s">
-        <v>314</v>
-      </c>
-      <c r="J131" t="s">
-        <v>299</v>
-      </c>
-      <c r="K131" t="s">
-        <v>299</v>
-      </c>
-      <c r="L131" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12">
-      <c r="A132" t="s">
-        <v>142</v>
-      </c>
-      <c r="B132" t="s">
-        <v>283</v>
-      </c>
-      <c r="D132">
-        <v>1</v>
-      </c>
-      <c r="E132" s="2">
-        <v>46041</v>
-      </c>
-      <c r="F132" s="2">
-        <v>46022</v>
-      </c>
-      <c r="H132" t="s">
-        <v>297</v>
-      </c>
-      <c r="I132" t="s">
-        <v>310</v>
-      </c>
-      <c r="J132" t="s">
-        <v>310</v>
-      </c>
-      <c r="K132" t="s">
-        <v>327</v>
-      </c>
-      <c r="L132" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12">
-      <c r="A133" t="s">
-        <v>143</v>
-      </c>
-      <c r="B133" t="s">
-        <v>284</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133" s="2">
-        <v>45826</v>
-      </c>
-      <c r="F133" s="2">
-        <v>46042</v>
-      </c>
-      <c r="G133">
-        <v>216</v>
-      </c>
-      <c r="H133" t="s">
-        <v>298</v>
-      </c>
-      <c r="I133" t="s">
-        <v>299</v>
-      </c>
-      <c r="J133" t="s">
-        <v>299</v>
-      </c>
-      <c r="K133" t="s">
-        <v>327</v>
-      </c>
-      <c r="L133" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12">
-      <c r="A134" t="s">
-        <v>144</v>
-      </c>
-      <c r="B134" t="s">
-        <v>285</v>
-      </c>
-      <c r="D134">
-        <v>1</v>
-      </c>
-      <c r="E134" s="2">
-        <v>45844</v>
-      </c>
-      <c r="F134" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G134">
-        <v>212</v>
-      </c>
-      <c r="H134" t="s">
-        <v>298</v>
-      </c>
-      <c r="I134" t="s">
-        <v>299</v>
-      </c>
-      <c r="J134" t="s">
-        <v>299</v>
-      </c>
-      <c r="K134" t="s">
-        <v>327</v>
-      </c>
-      <c r="L134" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12">
-      <c r="A135" t="s">
-        <v>145</v>
-      </c>
-      <c r="B135" t="s">
-        <v>286</v>
-      </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135" s="2">
-        <v>46036</v>
-      </c>
-      <c r="F135" s="2">
-        <v>46043</v>
-      </c>
-      <c r="H135" t="s">
-        <v>297</v>
-      </c>
-      <c r="I135" t="s">
-        <v>322</v>
-      </c>
-      <c r="J135" t="s">
-        <v>322</v>
-      </c>
-      <c r="K135" t="s">
-        <v>327</v>
-      </c>
-      <c r="L135" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12">
-      <c r="A136" t="s">
-        <v>146</v>
-      </c>
-      <c r="B136" t="s">
-        <v>287</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136" s="2">
-        <v>46058</v>
-      </c>
-      <c r="F136" s="2">
-        <v>45978</v>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136" t="s">
-        <v>298</v>
-      </c>
-      <c r="I136" t="s">
-        <v>323</v>
-      </c>
-      <c r="J136" t="s">
-        <v>323</v>
-      </c>
-      <c r="K136" t="s">
-        <v>327</v>
-      </c>
-      <c r="L136" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12">
-      <c r="A137" t="s">
-        <v>147</v>
-      </c>
-      <c r="B137" t="s">
-        <v>288</v>
-      </c>
-      <c r="D137">
-        <v>1</v>
-      </c>
-      <c r="E137" s="2">
-        <v>45986</v>
-      </c>
-      <c r="F137" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G137">
-        <v>70</v>
-      </c>
-      <c r="H137" t="s">
-        <v>298</v>
-      </c>
-      <c r="I137" t="s">
-        <v>299</v>
-      </c>
-      <c r="J137" t="s">
-        <v>299</v>
-      </c>
-      <c r="K137" t="s">
-        <v>327</v>
-      </c>
-      <c r="L137" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12">
-      <c r="A138" t="s">
-        <v>148</v>
-      </c>
-      <c r="B138" t="s">
-        <v>289</v>
-      </c>
-      <c r="D138">
-        <v>1</v>
-      </c>
-      <c r="E138" s="2">
-        <v>46037</v>
-      </c>
-      <c r="F138" s="2">
-        <v>46059</v>
-      </c>
-      <c r="G138">
-        <v>22</v>
-      </c>
-      <c r="H138" t="s">
-        <v>298</v>
-      </c>
-      <c r="I138" t="s">
-        <v>300</v>
-      </c>
-      <c r="J138" t="s">
-        <v>300</v>
-      </c>
-      <c r="K138" t="s">
-        <v>327</v>
-      </c>
-      <c r="L138" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12">
-      <c r="A139" t="s">
-        <v>149</v>
-      </c>
-      <c r="B139" t="s">
-        <v>290</v>
-      </c>
-      <c r="D139">
-        <v>1</v>
-      </c>
-      <c r="E139" s="2">
-        <v>45830</v>
-      </c>
-      <c r="F139" s="2">
-        <v>46052</v>
-      </c>
-      <c r="G139">
-        <v>222</v>
-      </c>
-      <c r="H139" t="s">
-        <v>298</v>
-      </c>
-      <c r="I139" t="s">
-        <v>299</v>
-      </c>
-      <c r="J139" t="s">
-        <v>299</v>
-      </c>
-      <c r="K139" t="s">
-        <v>327</v>
-      </c>
-      <c r="L139" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12">
-      <c r="A140" t="s">
-        <v>150</v>
-      </c>
-      <c r="B140" t="s">
-        <v>291</v>
-      </c>
-      <c r="D140">
-        <v>2</v>
-      </c>
-      <c r="E140" s="2">
-        <v>45980</v>
-      </c>
-      <c r="F140" s="2">
-        <v>45989</v>
-      </c>
-      <c r="G140">
-        <v>9</v>
-      </c>
-      <c r="H140" t="s">
-        <v>298</v>
-      </c>
-      <c r="I140" t="s">
-        <v>324</v>
-      </c>
-      <c r="J140" t="s">
-        <v>309</v>
-      </c>
-      <c r="K140" t="s">
-        <v>309</v>
-      </c>
-      <c r="L140" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12">
-      <c r="A141" t="s">
-        <v>151</v>
-      </c>
-      <c r="B141" t="s">
-        <v>292</v>
-      </c>
-      <c r="D141">
-        <v>1</v>
-      </c>
-      <c r="E141" s="2">
-        <v>45922</v>
-      </c>
-      <c r="F141" s="2">
-        <v>46041</v>
-      </c>
-      <c r="G141">
-        <v>119</v>
-      </c>
-      <c r="H141" t="s">
-        <v>298</v>
-      </c>
-      <c r="I141" t="s">
-        <v>299</v>
-      </c>
-      <c r="J141" t="s">
-        <v>299</v>
-      </c>
-      <c r="K141" t="s">
-        <v>327</v>
-      </c>
-      <c r="L141" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12">
-      <c r="A142" t="s">
-        <v>152</v>
-      </c>
-      <c r="B142" t="s">
-        <v>293</v>
-      </c>
-      <c r="D142">
-        <v>1</v>
-      </c>
-      <c r="E142" s="2">
-        <v>45973</v>
-      </c>
-      <c r="F142" s="2">
-        <v>46006</v>
-      </c>
-      <c r="H142" t="s">
-        <v>297</v>
-      </c>
-      <c r="I142" t="s">
-        <v>299</v>
-      </c>
-      <c r="J142" t="s">
-        <v>299</v>
-      </c>
-      <c r="K142" t="s">
-        <v>327</v>
-      </c>
-      <c r="L142" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12">
-      <c r="A143" t="s">
-        <v>153</v>
-      </c>
-      <c r="B143" t="s">
-        <v>294</v>
-      </c>
-      <c r="D143">
-        <v>1</v>
-      </c>
-      <c r="E143" s="2">
-        <v>45671</v>
-      </c>
-      <c r="F143" s="2">
-        <v>46008</v>
-      </c>
-      <c r="H143" t="s">
-        <v>297</v>
-      </c>
-      <c r="I143" t="s">
-        <v>299</v>
-      </c>
-      <c r="J143" t="s">
-        <v>299</v>
-      </c>
-      <c r="K143" t="s">
-        <v>327</v>
-      </c>
-      <c r="L143" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12">
-      <c r="A144" t="s">
-        <v>154</v>
-      </c>
-      <c r="B144" t="s">
-        <v>295</v>
-      </c>
-      <c r="D144">
-        <v>1</v>
-      </c>
-      <c r="E144" s="2">
-        <v>46072</v>
-      </c>
-      <c r="F144" s="2">
-        <v>46038</v>
-      </c>
-      <c r="H144" t="s">
-        <v>297</v>
-      </c>
-      <c r="I144" t="s">
-        <v>318</v>
-      </c>
-      <c r="J144" t="s">
-        <v>318</v>
-      </c>
-      <c r="K144" t="s">
-        <v>327</v>
-      </c>
-      <c r="L144" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12">
-      <c r="A145" t="s">
-        <v>155</v>
-      </c>
-      <c r="B145" t="s">
-        <v>226</v>
-      </c>
-      <c r="D145">
-        <v>1</v>
-      </c>
-      <c r="E145" s="2">
-        <v>45999</v>
-      </c>
-      <c r="F145" s="2">
-        <v>46002</v>
-      </c>
-      <c r="G145">
-        <v>3</v>
-      </c>
-      <c r="H145" t="s">
-        <v>298</v>
-      </c>
-      <c r="I145" t="s">
-        <v>299</v>
-      </c>
-      <c r="J145" t="s">
-        <v>299</v>
-      </c>
-      <c r="K145" t="s">
-        <v>327</v>
-      </c>
-      <c r="L145" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12">
-      <c r="A146" t="s">
-        <v>156</v>
-      </c>
-      <c r="B146" t="s">
-        <v>296</v>
-      </c>
-      <c r="D146">
-        <v>1</v>
-      </c>
-      <c r="E146" s="2">
-        <v>45963</v>
-      </c>
-      <c r="F146" s="2">
-        <v>46056</v>
-      </c>
-      <c r="G146">
-        <v>93</v>
-      </c>
-      <c r="H146" t="s">
-        <v>298</v>
-      </c>
-      <c r="I146" t="s">
-        <v>299</v>
-      </c>
-      <c r="J146" t="s">
-        <v>299</v>
-      </c>
-      <c r="K146" t="s">
-        <v>327</v>
-      </c>
-      <c r="L146" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
